--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M444"/>
+  <dimension ref="A1:M462"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -3058,8 +3058,12 @@
       <c r="A108" t="s">
         <v>238</v>
       </c>
-      <c r="B108" t="s">
-        <v>245</v>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
@@ -3722,8 +3726,12 @@
       <c r="A155" t="s">
         <v>238</v>
       </c>
-      <c r="B155" t="s">
-        <v>245</v>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
@@ -3835,14 +3843,20 @@
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A165" t="s">
-        <v>246</v>
-      </c>
-      <c r="B165" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C165" t="s">
-        <v>77</v>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D165" s="10">
         <v>1.08</v>
@@ -8149,6 +8163,387 @@
       </c>
       <c r="I444" s="32"/>
     </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+      <c r="B456">
+        <v>1</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>7N gallium production</t>
+        </is>
+      </c>
+      <c r="B457">
+        <v>0.5073997516391634</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>7N Gallium</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>7N Gallium</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>7N arsenic production</t>
+        </is>
+      </c>
+      <c r="B458">
+        <v>0.5452318273082052</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>7N Arsenic</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>7N Arsenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>boron carbide production</t>
+        </is>
+      </c>
+      <c r="B459">
+        <v>0.01</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>boron carbide</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>boron carbide</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>market group for electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="B460">
+        <v>50</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>UCTE</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>electricity, low voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>treatment of hazardous waste, underground deposit</t>
+        </is>
+      </c>
+      <c r="B461">
+        <v>-0.01</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>treatment of hazardous waste, underground deposit</t>
+        </is>
+      </c>
+      <c r="B462">
+        <v>-0.05263157894736836</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I444" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M462"/>
+  <dimension ref="A1:M475"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -1425,8 +1425,12 @@
       <c r="A6" t="s">
         <v>238</v>
       </c>
-      <c r="B6" t="s">
-        <v>241</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1542,14 +1546,20 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" t="s">
-        <v>77</v>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -2706,8 +2716,12 @@
       <c r="A87" t="s">
         <v>238</v>
       </c>
-      <c r="B87" t="s">
-        <v>241</v>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
@@ -7615,8 +7629,12 @@
       <c r="A412" t="s">
         <v>238</v>
       </c>
-      <c r="B412" t="s">
-        <v>241</v>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.2">
@@ -7844,8 +7862,8 @@
         <v>77</v>
       </c>
       <c r="D426" s="33">
-        <f>1/100</f>
-        <v>0.01</v>
+        <f>1</f>
+        <v>1</v>
       </c>
       <c r="E426" t="s">
         <v>19</v>
@@ -8541,6 +8559,212 @@
       <c r="I462" t="inlineStr">
         <is>
           <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B467">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+      <c r="B474">
+        <v>1</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>GaAs wafer production - cleaning, quality control, packing</t>
+        </is>
+      </c>
+      <c r="B475">
+        <v>0.01</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GaAs wafer </t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GaAs wafer </t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M475"/>
+  <dimension ref="A1:M517"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -7631,7 +7631,9 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.
+          <t>APPROVED GaAs-Si MODULE ASSEMBLY COVERAGE, issue77,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S1 states that nanowire transfer is followed by both Si-cell and module manufacture. Existing installation already supplies1m2 complete Si cells plus1m2 GaAs ELO afterissue76, but contains no glass/encapsulant/frame/module assembly. Add one1m2 assembly-only reference using the published-source-compatible architecture of the existing ecoinvent3.10 RER single-Si panel-production inventory, copied into this workbook as a scoped engineering adaptation. Copy every original non-cell technosphere ingredient, processing service, packaging, factory and existing waste exchange plus biosphere flows; exclude the single photovoltaic-cell market input so no second Si cell or wafer is purchased. Preserve existing separate mounting/electricalinstallation/inverter purchases. Important geometry assumption: retain original GaAs design1m2 active Si cell per1m2 nominal module/0.28kWp; native panel reference cell coverage is0.9324100017547607m2 per modulem2. This uses its per-module-area assembly burden, not a claim that its original frame/layout is a measured GaAs module. Active-area packing, module gaps and optical fill factor require design validation; do not silently change28% module power or lifetime electricity denominator. Retain source reference module glass/EVA/backsheet/AlMg3 frame/interconnections and manufacture burdens rather than adding only an aluminium filler. No change to native PV panels or existing2026PV reference design. Copied waste outputs stay in the original reference scope; no new GaAs nanowire-specific EOL recovery, treatment route or substitution credit is invented. Background3.10 suppliers are migrated by existing supported-version import logic. Exact prospective tandem encapsulation, reliability, assembly yield and nanolayer disposal remain gaps, not asserted solved by a silicon-module analogue. Source native process includes some legacy disposal assumptions; these are retained once and documented, not additional external recycling credits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Ex-ante LCA. Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
         </is>
@@ -7901,6 +7903,36 @@
         <v>16</v>
       </c>
       <c r="I427" s="28"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D428">
+        <v>1</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A429" s="2" t="s">
@@ -8765,6 +8797,1222 @@
       <c r="I475" t="inlineStr">
         <is>
           <t xml:space="preserve">GaAs wafer </t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B480">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs-Si MODULE ASSEMBLY COVERAGE, issue77,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S1 states that nanowire transfer is followed by both Si-cell and module manufacture. Existing installation already supplies1m2 complete Si cells plus1m2 GaAs ELO afterissue76, but contains no glass/encapsulant/frame/module assembly. Add one1m2 assembly-only reference using the published-source-compatible architecture of the existing ecoinvent3.10 RER single-Si panel-production inventory, copied into this workbook as a scoped engineering adaptation. Copy every original non-cell technosphere ingredient, processing service, packaging, factory and existing waste exchange plus biosphere flows; exclude the single photovoltaic-cell market input so no second Si cell or wafer is purchased. Preserve existing separate mounting/electricalinstallation/inverter purchases. Important geometry assumption: retain original GaAs design1m2 active Si cell per1m2 nominal module/0.28kWp; native panel reference cell coverage is0.9324100017547607m2 per modulem2. This uses its per-module-area assembly burden, not a claim that its original frame/layout is a measured GaAs module. Active-area packing, module gaps and optical fill factor require design validation; do not silently change28% module power or lifetime electricity denominator. Retain source reference module glass/EVA/backsheet/AlMg3 frame/interconnections and manufacture burdens rather than adding only an aluminium filler. No change to native PV panels or existing2026PV reference design. Copied waste outputs stay in the original reference scope; no new GaAs nanowire-specific EOL recovery, treatment route or substitution credit is invented. Background3.10 suppliers are migrated by existing supported-version import logic. Exact prospective tandem encapsulation, reliability, assembly yield and nanolayer disposal remain gaps, not asserted solved by a silicon-module analogue. Source native process includes some legacy disposal assumptions; these are retained once and documented, not additional external recycling credits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+      <c r="B487">
+        <v>1</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>market for 1-propanol</t>
+        </is>
+      </c>
+      <c r="B488">
+        <v>0.008138599805533886</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>1-propanol</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>1-propanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>market for acetone, liquid</t>
+        </is>
+      </c>
+      <c r="B489">
+        <v>0.01295899972319603</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>acetone, liquid</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>acetone, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>market for aluminium alloy, AlMg3</t>
+        </is>
+      </c>
+      <c r="B490">
+        <v>2.6294000148773193</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>aluminium alloy, AlMg3</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>aluminium alloy, AlMg3</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>market for brazing solder, cadmium free</t>
+        </is>
+      </c>
+      <c r="B491">
+        <v>0.008764700032770634</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>brazing solder, cadmium free</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>brazing solder, cadmium free</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B492">
+        <v>0.11269000172615051</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>market for corrugated board box</t>
+        </is>
+      </c>
+      <c r="B493">
+        <v>1.0956000089645386</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>corrugated board box</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B494">
+        <v>4.710700035095215</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>market for ethylvinylacetate, foil</t>
+        </is>
+      </c>
+      <c r="B495">
+        <v>1.0017000436782837</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ethylvinylacetate, foil</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>ethylvinylacetate, foil</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>market for glass fibre reinforced plastic, polyamide, injection moulded</t>
+        </is>
+      </c>
+      <c r="B496">
+        <v>0.1878100037574768</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyamide, injection moulded</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>glass fibre reinforced plastic, polyamide, injection moulded</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>market group for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B497">
+        <v>4.866390228271484</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>market for lubricating oil</t>
+        </is>
+      </c>
+      <c r="B498">
+        <v>0.0016069000121206045</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>lubricating oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>market for methanol</t>
+        </is>
+      </c>
+      <c r="B499">
+        <v>0.0021556001156568527</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>methanol</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>methanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>market group for municipal solid waste</t>
+        </is>
+      </c>
+      <c r="B500">
+        <v>-0.029999999329447746</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>municipal solid waste</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>municipal solid waste</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>market for nickel, class 1</t>
+        </is>
+      </c>
+      <c r="B501">
+        <v>0.00016276999667752534</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>nickel, class 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>market for photovoltaic panel factory</t>
+        </is>
+      </c>
+      <c r="B502">
+        <v>3.999999989900971e-06</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>photovoltaic panel factory</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>photovoltaic panel factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="B503">
+        <v>0.37297001481056213</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>market for polyvinylfluoride, film</t>
+        </is>
+      </c>
+      <c r="B504">
+        <v>0.1103999987244606</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>polyvinylfluoride, film</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>polyvinylfluoride, film</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>market for silicone product</t>
+        </is>
+      </c>
+      <c r="B505">
+        <v>0.12195000052452087</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>silicone product</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>market for solar glass, low-iron</t>
+        </is>
+      </c>
+      <c r="B506">
+        <v>10.079000473022461</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>solar glass, low-iron</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>solar glass, low-iron</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>market group for tap water</t>
+        </is>
+      </c>
+      <c r="B507">
+        <v>21.285999298095703</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>tempering, flat glass</t>
+        </is>
+      </c>
+      <c r="B508">
+        <v>10.079000473022461</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>tempering, flat glass</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>tempering, flat glass</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>market for vinyl acetate</t>
+        </is>
+      </c>
+      <c r="B509">
+        <v>0.0016434000572189689</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>vinyl acetate</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>vinyl acetate</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>market for waste mineral oil</t>
+        </is>
+      </c>
+      <c r="B510">
+        <v>-0.0015680805081501603</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>market for waste mineral oil</t>
+        </is>
+      </c>
+      <c r="B511">
+        <v>-3.8819438486825675e-05</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>waste mineral oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>market group for waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="B512">
+        <v>-1.6861000061035156</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>waste plastic, mixture</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>market for waste polyvinylfluoride</t>
+        </is>
+      </c>
+      <c r="B513">
+        <v>-0.1103999987244606</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>waste polyvinylfluoride</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>waste polyvinylfluoride</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B514">
+        <v>-0.020764166489243507</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B515">
+        <v>-0.0005218342412263155</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+      <c r="B516">
+        <v>0.11269000172615051</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B517">
+        <v>0.0031928999815136194</v>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M517"/>
+  <dimension ref="A1:M614"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -2359,8 +2359,12 @@
       <c r="A65" t="s">
         <v>238</v>
       </c>
-      <c r="B65" t="s">
-        <v>241</v>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
@@ -2615,14 +2619,20 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
-        <v>104</v>
-      </c>
-      <c r="B81" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" t="s">
-        <v>77</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D81" s="7">
         <v>8.4999999999999999E-6</v>
@@ -2636,8 +2646,10 @@
       <c r="G81" t="s">
         <v>16</v>
       </c>
-      <c r="I81" t="s">
-        <v>108</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
@@ -10016,6 +10028,1907 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B522">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B529">
+        <v>1</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>market for hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="B530">
+        <v>0.012457979038955904</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>market for bromine</t>
+        </is>
+      </c>
+      <c r="B531">
+        <v>0.9875420209610442</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>bromine</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>bromine</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B532">
+        <v>1</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B537">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B544">
+        <v>1</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>market for hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="B545">
+        <v>0.007880388831518929</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>market for iodine</t>
+        </is>
+      </c>
+      <c r="B546">
+        <v>0.9921196111684811</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B547">
+        <v>1</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B552">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="B559">
+        <v>1</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>market for ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="B560">
+        <v>0.422783253491915</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B561">
+        <v>0.742543545693152</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B562">
+        <v>-0.0001653267991850669</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B563">
+        <v>0.5</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B568">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="B575">
+        <v>1</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>market for ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="B576">
+        <v>0.2953775898114511</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B577">
+        <v>0.820128005718152</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B578">
+        <v>-0.00011550559552960325</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B579">
+        <v>0.5</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B584">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+      <c r="B591">
+        <v>1</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B592">
+        <v>0.33366155515394635</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>market for iodine</t>
+        </is>
+      </c>
+      <c r="B593">
+        <v>0.6663384448460538</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B594">
+        <v>1</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B599">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="B606">
+        <v>1</v>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>diethylzinc, organozinc synthesis engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B607">
+        <v>1.7696813421239639</v>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="B608">
+        <v>1.076556149792078</v>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>ethyl bromide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="B609">
+        <v>1.4304924182168708</v>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>ethyl iodide, ethanol route engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+      <c r="B610">
+        <v>0.029494689035399396</v>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>copper iodide, catalyst engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B611">
+        <v>-3.3062245991683117</v>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>market for nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B612">
+        <v>0.05</v>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>market for hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="B613">
+        <v>0.01</v>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B614">
+        <v>1</v>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I444" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M614"/>
+  <dimension ref="A1:M629"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -3524,8 +3524,12 @@
       <c r="A139" t="s">
         <v>238</v>
       </c>
-      <c r="B139" t="s">
-        <v>245</v>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
@@ -3635,19 +3639,30 @@
       <c r="G148" t="s">
         <v>10</v>
       </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A149" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B149" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C149" t="s">
-        <v>77</v>
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+      <c r="B149" s="9" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D149" s="10">
-        <v>1.4705881999999999</v>
+        <v>1</v>
       </c>
       <c r="E149" t="s">
         <v>5</v>
@@ -3658,8 +3673,10 @@
       <c r="G149" t="s">
         <v>16</v>
       </c>
-      <c r="I149" s="9" t="s">
-        <v>132</v>
+      <c r="I149" s="9" t="inlineStr">
+        <is>
+          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
@@ -3739,6 +3756,15 @@
       <c r="I152" t="s">
         <v>131</v>
       </c>
+    </row>
+    <row r="153">
+      <c r="A153"/>
+      <c r="B153"/>
+      <c r="C153"/>
+      <c r="D153"/>
+      <c r="E153"/>
+      <c r="G153"/>
+      <c r="I153"/>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
@@ -11929,6 +11955,277 @@
         </is>
       </c>
     </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B619">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+      <c r="B626">
+        <v>1</v>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>arsine production</t>
+        </is>
+      </c>
+      <c r="B627">
+        <v>1.5299443671611501</v>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>arsine</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>arsine</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>treatment of hazardous waste, underground deposit</t>
+        </is>
+      </c>
+      <c r="B628">
+        <v>-0.4705881999999999</v>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B629">
+        <v>0.05935616716115022</v>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I444" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M629"/>
+  <dimension ref="A1:M667"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -3780,7 +3780,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
         </is>
@@ -3893,6 +3898,14 @@
       <c r="G164" t="s">
         <v>10</v>
       </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
+        </is>
+      </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="inlineStr">
@@ -3951,14 +3964,20 @@
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A167" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="B167" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C167" t="s">
-        <v>77</v>
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
       <c r="D167" s="10">
         <v>0.01</v>
@@ -3972,8 +3991,13 @@
       <c r="G167" t="s">
         <v>16</v>
       </c>
-      <c r="I167" t="s">
-        <v>140</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
+        </is>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
@@ -8329,7 +8353,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.</t>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED GaAs BOULE MATERIAL BALANCE, issue75,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S6 outputs 1kg GaAs from0.236kg Ga and0.516kg As: only0.752kg feed, excluding the B4C process crucible. The problem is present in the published supplement, not simply an import typo. Attempts to recover Smith2018 original thesis https://repository.rit.edu/theses/9877/ returned HTTP403 for the full text; the original author batch calculation is not independently verified. Use a distinct balanced engineering reference, not a falsely claimed verbatim source correction. GaAs has one Ga and one As atom; atomic masses69.723 and74.921595 give retained fractions0.4820297640572052 and0.5179702359427949. Adopt95% overall boule-material retention as an explicit assumption, test90-100%; feed both7N elements at their retained fraction/0.95. Treat the corresponding1/0.95-1kg GaAs process loss with the existing hazardous underground-deposit proxy, not a recycling credit. Preserve source50kWh/kg process electricity,0.01kg B4C crucible and its paired0.01kg disposal. Existing upstream7N refining and downstream crystal-growth/wafer-sawing losses remain separate, not removed or charged twice. Route the active single-crystal producer to this new provider at its existing1.08kg/kg dose. Old provider identity remains available and is marked as a legacy unbalanced source recipe. Actual industrial yield, Ga/As-specific volatilization, recovery, purity and exhaust treatment are not established; underground disposal is a mixed-hazardous-waste fate proxy. No native database, runtime or YAML edits, and no primary-secondary-share claim.</t>
         </is>
       </c>
     </row>
@@ -8416,6 +8445,14 @@
           <t>polycrystalline GaAs boule, balanced engineering reference</t>
         </is>
       </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
+        </is>
+      </c>
       <c r="I456" t="inlineStr">
         <is>
           <t>polycrystalline GaAs boule, balanced engineering reference</t>
@@ -8495,7 +8532,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>boron carbide production</t>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
         </is>
       </c>
       <c r="B459">
@@ -8518,12 +8555,20 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>boron carbide</t>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>boron carbide</t>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
         </is>
       </c>
     </row>
@@ -12223,6 +12268,842 @@
       <c r="H629" t="inlineStr">
         <is>
           <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B634">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="B641">
+        <v>1</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>boric oxide production</t>
+        </is>
+      </c>
+      <c r="B642">
+        <v>0.29710225332878115</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B643">
+        <v>0.15377688630932057</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B644">
+        <v>0.9077330146807784</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B645">
+        <v>1</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B646">
+        <v>3</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Carbon monoxide, fossil</t>
+        </is>
+      </c>
+      <c r="B647">
+        <v>0.35861215431888016</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B652">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges. Feedkg={'BCl3': 9.938857701533118, 'NH3': 5.7790606184639985, 'H2SO4': 2.0798985415345594, 'water': 102.29235901536086, 'graphite': 0.02};brinesoluteskg={'boric_acid': 2.6226080170002315, 'ammonium_chloride': 13.61265516210238, 'ammonium_sulfate': 2.802281118842559};brinemass=119.03754429794517kg;density1100-&gt;0.10821594936176834m3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+      <c r="B659">
+        <v>1</v>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="B660">
+        <v>9.938857701533118</v>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>boron trichloride, carbochlorination engineering reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>market for ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+      <c r="B661">
+        <v>5.7790606184639985</v>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>ammonia, anhydrous, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>market for sulfuric acid</t>
+        </is>
+      </c>
+      <c r="B662">
+        <v>2.0798985415345594</v>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>sulfuric acid</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>sulfuric acid</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>market for tap water</t>
+        </is>
+      </c>
+      <c r="B663">
+        <v>102.29235901536086</v>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>tap water</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B664">
+        <v>0.02</v>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B665">
+        <v>250</v>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B666">
+        <v>-0.10821594936176834</v>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>market for inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="B667">
+        <v>-0.07263157894736837</v>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>inert waste, for final disposal</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -2361,7 +2361,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.
+          <t>APPROVED GaAs NANOWIRE PRECURSOR BUDGET, issue 115, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx Compound density 5.32 g/cm3: https://www.iue.tuwien.ac.at/phd/quay/node26.html , Table 3.2.
+Retain source geometry: 1 m2 substrate, nanowires occupying 10% of projected area, 1.5 micrometre height (180 nm diameter cancels when coverage is already specified). Volume is 1.5000000000000002e-07 m3 and retained GaAs is 0.0007980000000000001 kg. Treat GaAs as a stoichiometric compound with equal numbers of Ga and As atoms, not equal elemental volumes or equal elemental masses. Use compound density instead of separate elemental Ga/As densities. Retained Ga = 0.0003846597517176498 kg; As = 0.00041334024828235035 kg.
+Retain the source deposition utilizations 50% Ga and 15% As. Use TMGa molecular Ga fraction 0.6071951092068136 and AsH3 As fraction 0.9612037088176696. Thus buy 0.0012670054349421078 kg TMGa and 0.002866823785569036 kg AsH3 per m2 instead of 0.00148 and 0.00298 kg. TMGa production yield affects its upstream gross feed, not the Ga fraction of the finished molecule; do not apply that yield again here. The source's 50/15% utilizations and nanowire coverage remain ex-ante assumptions, not measured industrial performance; sensitivity is needed.
+Unretained elemental Ga = 0.0003846597517176498 kg and As = 0.0023422614069333186 kg. Preserve the existing aggregate hazardous-waste and carrier-gas inventories because source-specific off-gas capture/speciation and solid/liquid split are not recovered; these balances do not justify inventing a recovered-metal credit or elemental air emissions. Dopants, hydrogen carrier, etching, energy, substrate reuse and module lifetime are unchanged. No native/runtime edits.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.
 PREVIOUS NOTES (retained as history; the correction above takes precedence):
 Ex-ante LCA. Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
         </is>
@@ -2473,6 +2478,14 @@
       <c r="G74" t="s">
         <v>10</v>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs NANOWIRE PRECURSOR BUDGET, issue 115, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx Compound density 5.32 g/cm3: https://www.iue.tuwien.ac.at/phd/quay/node26.html , Table 3.2.
+Retain source geometry: 1 m2 substrate, nanowires occupying 10% of projected area, 1.5 micrometre height (180 nm diameter cancels when coverage is already specified). Volume is 1.5000000000000002e-07 m3 and retained GaAs is 0.0007980000000000001 kg. Treat GaAs as a stoichiometric compound with equal numbers of Ga and As atoms, not equal elemental volumes or equal elemental masses. Use compound density instead of separate elemental Ga/As densities. Retained Ga = 0.0003846597517176498 kg; As = 0.00041334024828235035 kg.
+Retain the source deposition utilizations 50% Ga and 15% As. Use TMGa molecular Ga fraction 0.6071951092068136 and AsH3 As fraction 0.9612037088176696. Thus buy 0.0012670054349421078 kg TMGa and 0.002866823785569036 kg AsH3 per m2 instead of 0.00148 and 0.00298 kg. TMGa production yield affects its upstream gross feed, not the Ga fraction of the finished molecule; do not apply that yield again here. The source's 50/15% utilizations and nanowire coverage remain ex-ante assumptions, not measured industrial performance; sensitivity is needed.
+Unretained elemental Ga = 0.0003846597517176498 kg and As = 0.0023422614069333186 kg. Preserve the existing aggregate hazardous-waste and carrier-gas inventories because source-specific off-gas capture/speciation and solid/liquid split are not recovered; these balances do not justify inventing a recovered-metal credit or elemental air emissions. Dopants, hydrogen carrier, etching, energy, substrate reuse and module lifetime are unchanged. No native/runtime edits.</t>
+        </is>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
@@ -2583,7 +2596,7 @@
         <v>77</v>
       </c>
       <c r="D79" s="7">
-        <v>1.48E-3</v>
+        <v>0.0012670054349421078</v>
       </c>
       <c r="E79" t="s">
         <v>5</v>
@@ -2593,6 +2606,14 @@
       </c>
       <c r="G79" t="s">
         <v>16</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs NANOWIRE PRECURSOR BUDGET, issue 115, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx Compound density 5.32 g/cm3: https://www.iue.tuwien.ac.at/phd/quay/node26.html , Table 3.2.
+Retain source geometry: 1 m2 substrate, nanowires occupying 10% of projected area, 1.5 micrometre height (180 nm diameter cancels when coverage is already specified). Volume is 1.5000000000000002e-07 m3 and retained GaAs is 0.0007980000000000001 kg. Treat GaAs as a stoichiometric compound with equal numbers of Ga and As atoms, not equal elemental volumes or equal elemental masses. Use compound density instead of separate elemental Ga/As densities. Retained Ga = 0.0003846597517176498 kg; As = 0.00041334024828235035 kg.
+Retain the source deposition utilizations 50% Ga and 15% As. Use TMGa molecular Ga fraction 0.6071951092068136 and AsH3 As fraction 0.9612037088176696. Thus buy 0.0012670054349421078 kg TMGa and 0.002866823785569036 kg AsH3 per m2 instead of 0.00148 and 0.00298 kg. TMGa production yield affects its upstream gross feed, not the Ga fraction of the finished molecule; do not apply that yield again here. The source's 50/15% utilizations and nanowire coverage remain ex-ante assumptions, not measured industrial performance; sensitivity is needed.
+Unretained elemental Ga = 0.0003846597517176498 kg and As = 0.0023422614069333186 kg. Preserve the existing aggregate hazardous-waste and carrier-gas inventories because source-specific off-gas capture/speciation and solid/liquid split are not recovered; these balances do not justify inventing a recovered-metal credit or elemental air emissions. Dopants, hydrogen carrier, etching, energy, substrate reuse and module lifetime are unchanged. No native/runtime edits.</t>
+        </is>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -2606,7 +2627,7 @@
         <v>77</v>
       </c>
       <c r="D80" s="7">
-        <v>2.98E-3</v>
+        <v>0.002866823785569036</v>
       </c>
       <c r="E80" t="s">
         <v>5</v>
@@ -2616,6 +2637,14 @@
       </c>
       <c r="G80" t="s">
         <v>16</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>APPROVED GaAs NANOWIRE PRECURSOR BUDGET, issue 115, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx Compound density 5.32 g/cm3: https://www.iue.tuwien.ac.at/phd/quay/node26.html , Table 3.2.
+Retain source geometry: 1 m2 substrate, nanowires occupying 10% of projected area, 1.5 micrometre height (180 nm diameter cancels when coverage is already specified). Volume is 1.5000000000000002e-07 m3 and retained GaAs is 0.0007980000000000001 kg. Treat GaAs as a stoichiometric compound with equal numbers of Ga and As atoms, not equal elemental volumes or equal elemental masses. Use compound density instead of separate elemental Ga/As densities. Retained Ga = 0.0003846597517176498 kg; As = 0.00041334024828235035 kg.
+Retain the source deposition utilizations 50% Ga and 15% As. Use TMGa molecular Ga fraction 0.6071951092068136 and AsH3 As fraction 0.9612037088176696. Thus buy 0.0012670054349421078 kg TMGa and 0.002866823785569036 kg AsH3 per m2 instead of 0.00148 and 0.00298 kg. TMGa production yield affects its upstream gross feed, not the Ga fraction of the finished molecule; do not apply that yield again here. The source's 50/15% utilizations and nanowire coverage remain ex-ante assumptions, not measured industrial performance; sensitivity is needed.
+Unretained elemental Ga = 0.0003846597517176498 kg and As = 0.0023422614069333186 kg. Preserve the existing aggregate hazardous-waste and carrier-gas inventories because source-specific off-gas capture/speciation and solid/liquid split are not recovered; these balances do not justify inventing a recovered-metal credit or elemental air emissions. Dopants, hydrogen carrier, etching, energy, substrate reuse and module lifetime are unchanged. No native/runtime edits.</t>
+        </is>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -3371,8 +3371,14 @@
       <c r="A125" t="s">
         <v>238</v>
       </c>
-      <c r="B125" t="s">
-        <v>245</v>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>APPROVED GALLIUM PURIFICATION REJECT ACCOUNTING, issue 116, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx
+The inherited 70% purification yield buys 1.4285714 kg semiconductor-grade gallium per 1 kg 7N product. Preserve this gross input and electricity exactly. Assign the remaining 0.42857140000000005 kg to a separately documented hazardous solid/reject collection and underground-disposal reference, with zero recovery credit. This closes the stated mass balance without assuming that missing metal is automatically recycled or buying it twice.
+Actual rejects may be recycled gallium-rich cuts, process residues or other forms. The source does not resolve the recycling loop, impurity content or treatment technology. Generic hazardous underground disposal is an explicit conservative fate proxy, not demonstrated industrial gallium waste management. Compare 0-100% recovery with a fully specified recovery burden in a later sensitivity; do not change current primary/secondary shares or reduce gross metal demand in this correction. No additional elemental Ga emission or complete product EOL is added.
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
@@ -3482,6 +3488,13 @@
       <c r="G134" t="s">
         <v>10</v>
       </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>APPROVED GALLIUM PURIFICATION REJECT ACCOUNTING, issue 116, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx
+The inherited 70% purification yield buys 1.4285714 kg semiconductor-grade gallium per 1 kg 7N product. Preserve this gross input and electricity exactly. Assign the remaining 0.42857140000000005 kg to a separately documented hazardous solid/reject collection and underground-disposal reference, with zero recovery credit. This closes the stated mass balance without assuming that missing metal is automatically recycled or buying it twice.
+Actual rejects may be recycled gallium-rich cuts, process residues or other forms. The source does not resolve the recycling loop, impurity content or treatment technology. Generic hazardous underground disposal is an explicit conservative fate proxy, not demonstrated industrial gallium waste management. Compare 0-100% recovery with a fully specified recovery burden in a later sensitivity; do not change current primary/secondary shares or reduce gross metal demand in this correction. No additional elemental Ga emission or complete product EOL is added.</t>
+        </is>
+      </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="9" t="s">
@@ -3536,10 +3549,41 @@
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A137" s="9"/>
-      <c r="B137" s="9"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="10"/>
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>treatment of hazardous waste, underground deposit</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D137" s="10">
+        <v>-0.42857140000000005</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>APPROVED GALLIUM PURIFICATION REJECT ACCOUNTING, issue 116, 2026-10-19. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting information S3, S4 and S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx
+The inherited 70% purification yield buys 1.4285714 kg semiconductor-grade gallium per 1 kg 7N product. Preserve this gross input and electricity exactly. Assign the remaining 0.42857140000000005 kg to a separately documented hazardous solid/reject collection and underground-disposal reference, with zero recovery credit. This closes the stated mass balance without assuming that missing metal is automatically recycled or buying it twice.
+Actual rejects may be recycled gallium-rich cuts, process residues or other forms. The source does not resolve the recycling loop, impurity content or treatment technology. Generic hazardous underground disposal is an explicit conservative fate proxy, not demonstrated industrial gallium waste management. Compare 0-100% recovery with a fully specified recovery burden in a later sensitivity; do not change current primary/secondary shares or reduce gross metal demand in this correction. No additional elemental Ga emission or complete product EOL is added.</t>
+        </is>
+      </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1548,12 +1548,12 @@
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2650,12 +2650,12 @@
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3721,12 +3721,12 @@
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3983,12 +3983,12 @@
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule production, polycrystalline</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule, polycrystalline</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4039,12 +4039,12 @@
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -8042,12 +8042,12 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -8356,7 +8356,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule production, polycrystalline</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule, polycrystalline</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,8 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: polycrystalline GaAs boule, balanced engineering reference. Former reference product: polycrystalline GaAs boule, balanced engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
  CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
  Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
  BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.
@@ -8492,7 +8493,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule production, polycrystalline</t>
         </is>
       </c>
       <c r="B456">
@@ -8515,7 +8516,7 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule, polycrystalline</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -8528,7 +8529,7 @@
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>polycrystalline GaAs boule, balanced engineering reference</t>
+          <t xml:space="preserve">gallium arsenide boule, polycrystalline</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8606,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
       <c r="B459">
@@ -8628,7 +8629,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -8641,7 +8642,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
     </row>
@@ -8758,7 +8759,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8793,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8829,8 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: GaAs substrate manufacture, 100-use attribution reference. Former reference product: GaAs substrate manufacture, 100-use attribution reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8891,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
         </is>
       </c>
       <c r="B474">
@@ -8912,12 +8914,12 @@
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>GaAs substrate manufacture, 100-use attribution reference</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8966,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
     </row>
@@ -8998,7 +9000,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9036,8 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>APPROVED GaAs-Si MODULE ASSEMBLY COVERAGE, issue77,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S1 states that nanowire transfer is followed by both Si-cell and module manufacture. Existing installation already supplies1m2 complete Si cells plus1m2 GaAs ELO afterissue76, but contains no glass/encapsulant/frame/module assembly. Add one1m2 assembly-only reference using the published-source-compatible architecture of the existing ecoinvent3.10 RER single-Si panel-production inventory, copied into this workbook as a scoped engineering adaptation. Copy every original non-cell technosphere ingredient, processing service, packaging, factory and existing waste exchange plus biosphere flows; exclude the single photovoltaic-cell market input so no second Si cell or wafer is purchased. Preserve existing separate mounting/electricalinstallation/inverter purchases. Important geometry assumption: retain original GaAs design1m2 active Si cell per1m2 nominal module/0.28kWp; native panel reference cell coverage is0.9324100017547607m2 per modulem2. This uses its per-module-area assembly burden, not a claim that its original frame/layout is a measured GaAs module. Active-area packing, module gaps and optical fill factor require design validation; do not silently change28% module power or lifetime electricity denominator. Retain source reference module glass/EVA/backsheet/AlMg3 frame/interconnections and manufacture burdens rather than adding only an aluminium filler. No change to native PV panels or existing2026PV reference design. Copied waste outputs stay in the original reference scope; no new GaAs nanowire-specific EOL recovery, treatment route or substitution credit is invented. Background3.10 suppliers are migrated by existing supported-version import logic. Exact prospective tandem encapsulation, reliability, assembly yield and nanolayer disposal remain gaps, not asserted solved by a silicon-module analogue. Source native process includes some legacy disposal assumptions; these are retained once and documented, not additional external recycling credits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: photovoltaic module assembly only, GaAs-Si tandem reference. Former reference product: photovoltaic module assembly only, GaAs-Si tandem reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED GaAs-Si MODULE ASSEMBLY COVERAGE, issue77,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S1 states that nanowire transfer is followed by both Si-cell and module manufacture. Existing installation already supplies1m2 complete Si cells plus1m2 GaAs ELO afterissue76, but contains no glass/encapsulant/frame/module assembly. Add one1m2 assembly-only reference using the published-source-compatible architecture of the existing ecoinvent3.10 RER single-Si panel-production inventory, copied into this workbook as a scoped engineering adaptation. Copy every original non-cell technosphere ingredient, processing service, packaging, factory and existing waste exchange plus biosphere flows; exclude the single photovoltaic-cell market input so no second Si cell or wafer is purchased. Preserve existing separate mounting/electricalinstallation/inverter purchases. Important geometry assumption: retain original GaAs design1m2 active Si cell per1m2 nominal module/0.28kWp; native panel reference cell coverage is0.9324100017547607m2 per modulem2. This uses its per-module-area assembly burden, not a claim that its original frame/layout is a measured GaAs module. Active-area packing, module gaps and optical fill factor require design validation; do not silently change28% module power or lifetime electricity denominator. Retain source reference module glass/EVA/backsheet/AlMg3 frame/interconnections and manufacture burdens rather than adding only an aluminium filler. No change to native PV panels or existing2026PV reference design. Copied waste outputs stay in the original reference scope; no new GaAs nanowire-specific EOL recovery, treatment route or substitution credit is invented. Background3.10 suppliers are migrated by existing supported-version import logic. Exact prospective tandem encapsulation, reliability, assembly yield and nanolayer disposal remain gaps, not asserted solved by a silicon-module analogue. Source native process includes some legacy disposal assumptions; these are retained once and documented, not additional external recycling credits.</t>
         </is>
       </c>
     </row>
@@ -9095,7 +9098,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
       <c r="B487">
@@ -9118,12 +9121,12 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>photovoltaic module assembly only, GaAs-Si tandem reference</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10183,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
         </is>
       </c>
     </row>
@@ -10214,7 +10217,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide</t>
         </is>
       </c>
     </row>
@@ -10250,7 +10253,8 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen bromide, elemental synthesis engineering reference. Former reference product: hydrogen bromide, elemental synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10315,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
         </is>
       </c>
       <c r="B529">
@@ -10334,12 +10338,12 @@
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10460,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10494,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10530,8 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen iodide, elemental synthesis engineering reference. Former reference product: hydrogen iodide, elemental synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -10587,7 +10592,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
         </is>
       </c>
       <c r="B544">
@@ -10610,12 +10615,12 @@
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10737,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10771,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
     </row>
@@ -10802,7 +10807,8 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: ethyl bromide, ethanol route engineering reference. Former reference product: ethyl bromide, ethanol route engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10869,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
         </is>
       </c>
       <c r="B559">
@@ -10886,12 +10892,12 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10939,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
         </is>
       </c>
       <c r="B561">
@@ -10956,12 +10962,12 @@
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
         <is>
-          <t>hydrogen bromide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen bromide</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11049,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
         </is>
       </c>
     </row>
@@ -11077,7 +11083,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
     </row>
@@ -11113,7 +11119,8 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: ethyl iodide, ethanol route engineering reference. Former reference product: ethyl iodide, ethanol route engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -11174,7 +11181,7 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
         </is>
       </c>
       <c r="B575">
@@ -11197,12 +11204,12 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11251,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
         </is>
       </c>
       <c r="B577">
@@ -11267,12 +11274,12 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
         <is>
-          <t>hydrogen iodide, elemental synthesis engineering reference</t>
+          <t xml:space="preserve">hydrogen iodide</t>
         </is>
       </c>
     </row>
@@ -11354,7 +11361,7 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide production, for catalysts</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11395,7 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11431,8 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: copper iodide, catalyst engineering reference. Former reference product: copper iodide, catalyst engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -11485,7 +11493,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide production, for catalysts</t>
         </is>
       </c>
       <c r="B591">
@@ -11508,12 +11516,12 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
         </is>
       </c>
     </row>
@@ -11630,7 +11638,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11672,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11708,8 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: diethylzinc, organozinc synthesis engineering reference. Former reference product: diethylzinc, organozinc synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
@@ -11761,7 +11770,7 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
         </is>
       </c>
       <c r="B606">
@@ -11784,12 +11793,12 @@
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>diethylzinc, organozinc synthesis engineering reference</t>
+          <t xml:space="preserve">diethylzinc</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11840,7 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
         </is>
       </c>
       <c r="B608">
@@ -11854,19 +11863,19 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>ethyl bromide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
         </is>
       </c>
       <c r="B609">
@@ -11889,19 +11898,19 @@
       </c>
       <c r="G609" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>ethyl iodide, ethanol route engineering reference</t>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide production, for catalysts</t>
         </is>
       </c>
       <c r="B610">
@@ -11924,12 +11933,12 @@
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>copper iodide, catalyst engineering reference</t>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
         </is>
       </c>
     </row>
@@ -12081,7 +12090,7 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
         </is>
       </c>
     </row>
@@ -12115,7 +12124,7 @@
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12160,8 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: arsine-to-arsenic purification, source-yield engineering reference. Former reference product: arsine-to-arsenic purification, source-yield engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
         </is>
       </c>
     </row>
@@ -12212,7 +12222,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
         </is>
       </c>
       <c r="B626">
@@ -12235,12 +12245,12 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>arsine-to-arsenic purification, source-yield engineering reference</t>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
         </is>
       </c>
     </row>
@@ -12352,7 +12362,7 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
+          <t xml:space="preserve">boron trichloride production, carbochlorination</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12396,7 @@
       </c>
       <c r="B635" t="inlineStr">
         <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
+          <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
     </row>
@@ -12421,6 +12431,304 @@
         </is>
       </c>
       <c r="B638" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: boron trichloride, carbochlorination engineering reference. Former reference product: boron trichloride, carbochlorination engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+ CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
+ Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
+ BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boron trichloride production, carbochlorination</t>
+        </is>
+      </c>
+      <c r="B641">
+        <v>1</v>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boron trichloride</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boron trichloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>boric oxide production</t>
+        </is>
+      </c>
+      <c r="B642">
+        <v>0.29710225332878115</v>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>boric oxide</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>market for graphite</t>
+        </is>
+      </c>
+      <c r="B643">
+        <v>0.15377688630932057</v>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>graphite</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>market for chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="B644">
+        <v>0.9077330146807784</v>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>chlorine, liquid</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B645">
+        <v>1</v>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>market for heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="B646">
+        <v>3</v>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>megajoule</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>heat, district or industrial, natural gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Carbon monoxide, fossil</t>
+        </is>
+      </c>
+      <c r="B647">
+        <v>0.35861215431888016</v>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
         <is>
           <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
  CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
@@ -12429,303 +12737,6 @@
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B640" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C640" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D640" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E640" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F640" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G640" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H640" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I640" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
-        </is>
-      </c>
-      <c r="B641">
-        <v>1</v>
-      </c>
-      <c r="C641" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D641" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F641" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G641" t="inlineStr">
-        <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
-        </is>
-      </c>
-      <c r="I641" t="inlineStr">
-        <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>boric oxide production</t>
-        </is>
-      </c>
-      <c r="B642">
-        <v>0.29710225332878115</v>
-      </c>
-      <c r="C642" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D642" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F642" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G642" t="inlineStr">
-        <is>
-          <t>boric oxide</t>
-        </is>
-      </c>
-      <c r="I642" t="inlineStr">
-        <is>
-          <t>boric oxide</t>
-        </is>
-      </c>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>market for graphite</t>
-        </is>
-      </c>
-      <c r="B643">
-        <v>0.15377688630932057</v>
-      </c>
-      <c r="C643" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D643" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F643" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G643" t="inlineStr">
-        <is>
-          <t>graphite</t>
-        </is>
-      </c>
-      <c r="I643" t="inlineStr">
-        <is>
-          <t>graphite</t>
-        </is>
-      </c>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>market for chlorine, liquid</t>
-        </is>
-      </c>
-      <c r="B644">
-        <v>0.9077330146807784</v>
-      </c>
-      <c r="C644" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D644" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F644" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G644" t="inlineStr">
-        <is>
-          <t>chlorine, liquid</t>
-        </is>
-      </c>
-      <c r="I644" t="inlineStr">
-        <is>
-          <t>chlorine, liquid</t>
-        </is>
-      </c>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B645">
-        <v>1</v>
-      </c>
-      <c r="C645" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D645" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F645" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G645" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I645" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>market for heat, district or industrial, natural gas</t>
-        </is>
-      </c>
-      <c r="B646">
-        <v>3</v>
-      </c>
-      <c r="C646" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D646" t="inlineStr">
-        <is>
-          <t>megajoule</t>
-        </is>
-      </c>
-      <c r="F646" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G646" t="inlineStr">
-        <is>
-          <t>heat, district or industrial, natural gas</t>
-        </is>
-      </c>
-      <c r="I646" t="inlineStr">
-        <is>
-          <t>heat, district or industrial, natural gas</t>
-        </is>
-      </c>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>Carbon monoxide, fossil</t>
-        </is>
-      </c>
-      <c r="B647">
-        <v>0.35861215431888016</v>
-      </c>
-      <c r="D647" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="E647" t="inlineStr">
-        <is>
-          <t>air::non-urban air or from high stacks</t>
-        </is>
-      </c>
-      <c r="F647" t="inlineStr">
-        <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H647" t="inlineStr">
-        <is>
-          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
- CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
- Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
- BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
-        </is>
-      </c>
-    </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
@@ -12734,7 +12745,7 @@
       </c>
       <c r="B650" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12779,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12815,8 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
+          <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: pyrolytic boron nitride crucible, CVD engineering reference. Former reference product: pyrolytic boron nitride crucible, CVD engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
+APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
  CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
  Select25kWfurnace*20h/2kgfinishedbatch=250kWh/kgpBN,explicitengineeringutilitynotpatentmeasuredpower. Test100-1000kWh/kg;finishedbatchmassanddepositionareaareassumed,notrecoveredcommercialplantdata. Retainnonconsumedgraphitemandrelas2kgtool/kgperbatch with100productiveuses=.02kgfreshtool/kgpBN andequalspenttoolmass;reuse10-500uses sensitivity. Mandrelgeometry/roughnessandpuritynotvalidated. Scrub100kgwashwater/kgpBNplusstoichiometrichydrolysiswater;assumebrinedensity1100kg/m3,test1000-1250. Capturedbrineboricacid,NH4Cl,andammoniumsulfatecompositionexplicitbelow. Genericindustrial-averageWWT isUNVALIDATEDforhighsalinity/boron/ammonia;itrepresentscollection/treatmentdemand,notprovenremovalefficiencyorcorrectliquidelementemissions. No fictitiousmetalsrecoveryorhalidesubstitutioncredits.
  BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges. Feedkg={'BCl3': 9.938857701533118, 'NH3': 5.7790606184639985, 'H2SO4': 2.0798985415345594, 'water': 102.29235901536086, 'graphite': 0.02};brinesoluteskg={'boric_acid': 2.6226080170002315, 'ammonium_chloride': 13.61265516210238, 'ammonium_sulfate': 2.802281118842559};brinemass=119.03754429794517kg;density1100-&gt;0.10821594936176834m3.</t>
@@ -12868,7 +12880,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
       <c r="B659">
@@ -12891,19 +12903,19 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>pyrolytic boron nitride crucible, CVD engineering reference</t>
+          <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
+          <t xml:space="preserve">boron trichloride production, carbochlorination</t>
         </is>
       </c>
       <c r="B660">
@@ -12926,12 +12938,12 @@
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
+          <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>boron trichloride, carbochlorination engineering reference</t>
+          <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
     </row>

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -7043,8 +7043,12 @@
       <c r="A362" t="s">
         <v>238</v>
       </c>
-      <c r="B362" t="s">
-        <v>245</v>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>METHANE EMISSION IDENTITY REPAIR,2026-10-20. Pallas et al.2020 DOI10.1007/s11367-020-01791-z,supportingS7,Table Methyl aluminum sesquichloride production(Smith2018),identifies0.023kg methane emissions to air,not bromomethane. The previous workbook comment explicitly recorded substitution of methane by Methane,bromo-,Halon1001 (CH3Br). Correct that species to CH4 at exactly the same0.023kg and generic air compartment. No bromine-bearing feed is represented. The retained native methylchloride supplier uses methanol; select fossil methane as the conventional-feed reference. Pallas does not state carbon origin; test non-fossil methane separately. Mueller2021 labels its corresponding flow non-fossil,which is a separate source convention and does not make bromomethane correct. No technosphere input,product amount,other emission(including chlorine),manufacturing yield,equipment dose or disposal coefficient changes. This repairs a supplemental inventory mapping,not an ecoinvent-native recipe. It does not validate source mass closure,chemical purity,offgas capture or industrial process performance. PERC/TOPCon purified TMA in the separate2026PV workbook is unchanged. Source:https://media.springernature.com/original/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.2">
@@ -7254,8 +7258,10 @@
       </c>
     </row>
     <row r="376" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A376" s="22" t="s">
-        <v>207</v>
+      <c r="A376" s="22" t="inlineStr">
+        <is>
+          <t>Methane, fossil</t>
+        </is>
       </c>
       <c r="B376" s="22"/>
       <c r="C376"/>
@@ -7274,8 +7280,10 @@
       <c r="H376" t="s">
         <v>92</v>
       </c>
-      <c r="I376" t="s">
-        <v>215</v>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>METHANE IDENTITY CORRECTION,2026-10-20. Pallas2020 supportingS7 reports0.023kg methane to air perkg methylaluminium sesquichloride. The former adaptation mapped methane to bromomethane/Halon1001, which is CH3Br,not CH4. Keep source amount and generic air compartment. Use fossil methane for the retained conventional methanol-derived methylchloride feed; source-specific carbon origin remains unreported. A non-fossil-methane sensitivity changes carbon origin,not gas identity.</t>
+        </is>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -5231,8 +5231,12 @@
       <c r="A242" t="s">
         <v>238</v>
       </c>
-      <c r="B242" t="s">
-        <v>245</v>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>GLYCOL IDENTITY CORRECTION, 2026-10-20. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting S6, Sawing slurry production (Smith 2018), names polyethylene glycol (tri-ethylene glycol), 0.5 kg per kg slurry, alongside 0.5 kg silica sand. Its ecoinvent input column uses ethylene glycol as a proxy; the former supplemental adaptation instead selected diethylene glycol. Select the available triethylene-glycol market to match the specifically named molecular feed, without changing the 0.5 kg dose, silica sand, product mass or any slurry purchaser. Triethylene glycol (C6H14O4) and diethylene glycol (C4H10O3) are distinct chemicals. The loose polyethylene-glycol label does not establish a polymer molecular-weight distribution; this reference follows the explicit tri-ethylene qualifier, not a documented modern supplier assay. Retain ethylene- and diethylene-glycol alternatives as source/proxy sensitivities. No change to wafer yield, slurry recovery, discharge chemistry or final energy/equipment doses. This is a supplemental supplier mapping correction, not a defect in either native glycol-production inventory. Source: https://media.springernature.com/original/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx
+PREVIOUS NOTES (retained as history; the correction above takes precedence):
+Ex-ante LCA. Original inventory from Smith et al. (2018). Imported following Pallas et al. (2020) Ex ante life cycle assessment of GaAs/Si nanowire–based tandem solar cells: a benchmark for industrialization. The International Journal of Life Cycle Assessment, 25, 1767-1782. https://doi.org/10.1007/s11367-020-01791-z</t>
+        </is>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
@@ -5370,11 +5374,15 @@
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A253" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="B253" s="9" t="s">
-        <v>160</v>
+      <c r="A253" s="9" t="inlineStr">
+        <is>
+          <t>market for triethylene glycol</t>
+        </is>
+      </c>
+      <c r="B253" s="9" t="inlineStr">
+        <is>
+          <t>triethylene glycol</t>
+        </is>
       </c>
       <c r="C253" t="s">
         <v>73</v>
@@ -5391,8 +5399,10 @@
       <c r="G253" t="s">
         <v>16</v>
       </c>
-      <c r="I253" s="9" t="s">
-        <v>159</v>
+      <c r="I253" s="9" t="inlineStr">
+        <is>
+          <t>GLYCOL IDENTITY CORRECTION, 2026-10-20. Pallas et al. (2020), DOI 10.1007/s11367-020-01791-z, supporting S6, Sawing slurry production (Smith 2018), names polyethylene glycol (tri-ethylene glycol), 0.5 kg per kg slurry, alongside 0.5 kg silica sand. Its ecoinvent input column uses ethylene glycol as a proxy; the former supplemental adaptation instead selected diethylene glycol. Select the available triethylene-glycol market to match the specifically named molecular feed, without changing the 0.5 kg dose, silica sand, product mass or any slurry purchaser. Triethylene glycol (C6H14O4) and diethylene glycol (C4H10O3) are distinct chemicals. The loose polyethylene-glycol label does not establish a polymer molecular-weight distribution; this reference follows the explicit tri-ethylene qualifier, not a documented modern supplier assay. Retain ethylene- and diethylene-glycol alternatives as source/proxy sensitivities. No change to wafer yield, slurry recovery, discharge chemistry or final energy/equipment doses. This is a supplemental supplier mapping correction, not a defect in either native glycol-production inventory. Source: https://media.springernature.com/original/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx</t>
+        </is>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">

--- a/premise/data/additional_inventories/lci-PV-GaAs.xlsx
+++ b/premise/data/additional_inventories/lci-PV-GaAs.xlsx
@@ -1390,7 +1390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M667"/>
+  <dimension ref="A1:M679"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="71.6640625" customWidth="1"/>
@@ -8457,87 +8457,99 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Exchanges</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G455" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I455" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
           <t xml:space="preserve">gallium arsenide boule production, polycrystalline</t>
         </is>
       </c>
-      <c r="B456">
-        <v>1</v>
-      </c>
-      <c r="C456" t="inlineStr">
+      <c r="B457">
+        <v>1</v>
+      </c>
+      <c r="C457" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr">
+      <c r="D457" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F456" t="inlineStr">
+      <c r="F457" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr">
+      <c r="G457" t="inlineStr">
         <is>
           <t xml:space="preserve">gallium arsenide boule, polycrystalline</t>
         </is>
       </c>
-      <c r="H456" t="inlineStr">
+      <c r="H457" t="inlineStr">
         <is>
           <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
  CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
@@ -8545,55 +8557,20 @@
  BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
         </is>
       </c>
-      <c r="I456" t="inlineStr">
+      <c r="I457" t="inlineStr">
         <is>
           <t xml:space="preserve">gallium arsenide boule, polycrystalline</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>7N gallium production</t>
-        </is>
-      </c>
-      <c r="B457">
-        <v>0.5073997516391634</v>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G457" t="inlineStr">
-        <is>
-          <t>7N Gallium</t>
-        </is>
-      </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>7N Gallium</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>7N arsenic production</t>
+          <t>7N gallium production</t>
         </is>
       </c>
       <c r="B458">
-        <v>0.5452318273082052</v>
+        <v>0.5073997516391634</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
@@ -8612,45 +8589,80 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>7N Arsenic</t>
+          <t>7N Gallium</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>7N Arsenic</t>
+          <t>7N Gallium</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
+          <t>7N arsenic production</t>
+        </is>
+      </c>
+      <c r="B459">
+        <v>0.5452318273082052</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>7N Arsenic</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>7N Arsenic</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
-      <c r="B459">
+      <c r="B460">
         <v>0.01</v>
       </c>
-      <c r="C459" t="inlineStr">
+      <c r="C460" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr">
+      <c r="D460" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F459" t="inlineStr">
+      <c r="F460" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G459" t="inlineStr">
+      <c r="G460" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
-      <c r="H459" t="inlineStr">
+      <c r="H460" t="inlineStr">
         <is>
           <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
  CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
@@ -8658,64 +8670,29 @@
  BuildmissingBCl3viaB2O3+3C+3Cl2-&gt;2BCl3+3CO.100%stoichiometricconversionand1kWh+3MJ/kgBCl3areengineeringlower-boundprecursorsupplyreferences;semiconductorgradepurification,reagentexcess,phosgenepurificationandplantyieldunknown. COplacedasstoichiometricairoutputinthisreference;actualthermaloxidation/abatementmustbesensitivityreviewed,notclaimedmeasuredindustrialemissions. Boricoxideandgraphitesuppliersarefeed-gradeproxies. No silentlypurchasedbulkBNpowderandclaimCVDmanufacture. Existingworkbookonly;no runtime/native/primarysecondarychanges.</t>
         </is>
       </c>
-      <c r="I459" t="inlineStr">
+      <c r="I460" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible</t>
-        </is>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>market group for electricity, low voltage</t>
-        </is>
-      </c>
-      <c r="B460">
-        <v>50</v>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>UCTE</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>electricity, low voltage</t>
-        </is>
-      </c>
-      <c r="I460" t="inlineStr">
-        <is>
-          <t>electricity, low voltage</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>treatment of hazardous waste, underground deposit</t>
+          <t>market group for electricity, low voltage</t>
         </is>
       </c>
       <c r="B461">
-        <v>-0.01</v>
+        <v>50</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>RoW</t>
+          <t>UCTE</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -8725,12 +8702,12 @@
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>hazardous waste, for underground deposit</t>
+          <t>electricity, low voltage</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>hazardous waste, for underground deposit</t>
+          <t>electricity, low voltage</t>
         </is>
       </c>
     </row>
@@ -8741,526 +8718,480 @@
         </is>
       </c>
       <c r="B462">
+        <v>-0.01</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>treatment of hazardous waste, underground deposit</t>
+        </is>
+      </c>
+      <c r="B463">
         <v>-0.05263157894736836</v>
       </c>
-      <c r="C462" t="inlineStr">
+      <c r="C463" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr">
+      <c r="D463" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr">
+      <c r="F463" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr">
+      <c r="G463" t="inlineStr">
         <is>
           <t>hazardous waste, for underground deposit</t>
         </is>
       </c>
-      <c r="I462" t="inlineStr">
+      <c r="I463" t="inlineStr">
         <is>
           <t>hazardous waste, for underground deposit</t>
-        </is>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B465" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>location</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B467">
-        <v>1</v>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B468" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B468">
+        <v>1</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>square meter</t>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+          <t>square meter</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B471" t="inlineStr">
+      <c r="B472" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: GaAs substrate manufacture, 100-use attribution reference. Former reference product: GaAs substrate manufacture, 100-use attribution reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED GaAs SUBSTRATE REUSE BOUNDARY, issue76,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Paper sections2.7-2.10 distinguish baseline100 uses of a625um substrate from recurring lithography, gold patterning, wet etching, MOVPE growth and lift-off/CMP. The installation formerly bought0.01m2 of the entire ELO chain: fresh gold, precursors, solvents, growth and lift-off were all divided by100. New attribution helper supplies the manufacturing burden of0.01m2 complete original GaAs substrate per1m2 processed area, with no circulating technosphere loop or negative substitution credit. Its input includes the original wafer-production cleanup/quality/packaging chain and its source yields; issue75 already corrects the active boule recipe. Coating buys1m2 of this attributed substrate reference; all downstream process areas stay1m2, and the installation now buys1m2 ELO output per1m2 Si cell. Retain baseline CMP after every ELO: source optimization with one CMP per10ELO is a separate scenario, not silently adopted. Preserve source fresh gold169mg/m2; the paper90% gold recovery is another optimization scenario and is not imposed here. Keep source reagent quantities and electricity per processed area, no100x substrate-manufacture penalty. Original100-use baseline is prospective, not proven commercial durability; sensitivity10,100,500 uses applies to substrate manufacture only. Initial/final re-polishing count differs by at mostone over100cycles; baseline uses per-cycle source processing, not an invented recovered-wafer product or full annual substrate replacement. Fragility/attrition and route-specific recovery are gaps. Operating electricity output/lifetime,0.28kWp identity, Si cell input and BOS remain unchanged. No runtime/YAML/native edits or primary-secondary-share changes.</t>
         </is>
       </c>
     </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>name</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E473" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G473" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H473" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I473" t="inlineStr">
-        <is>
-          <t>product</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
-        </is>
-      </c>
-      <c r="B474">
-        <v>1</v>
-      </c>
-      <c r="C474" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>square meter</t>
-        </is>
-      </c>
-      <c r="F474" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G474" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
-        </is>
-      </c>
-      <c r="I474" t="inlineStr">
-        <is>
-          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cell production</t>
+        </is>
+      </c>
+      <c r="B476">
+        <v>1</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gallium arsenide substrate preparation, for photovoltaic cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
           <t>GaAs wafer production - cleaning, quality control, packing</t>
         </is>
       </c>
-      <c r="B475">
+      <c r="B477">
         <v>0.01</v>
       </c>
-      <c r="C475" t="inlineStr">
+      <c r="C477" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
+      <c r="D477" t="inlineStr">
         <is>
           <t>square meter</t>
         </is>
       </c>
-      <c r="F475" t="inlineStr">
+      <c r="F477" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G475" t="inlineStr">
+      <c r="G477" t="inlineStr">
         <is>
           <t xml:space="preserve">GaAs wafer </t>
         </is>
       </c>
-      <c r="I475" t="inlineStr">
+      <c r="I477" t="inlineStr">
         <is>
           <t xml:space="preserve">GaAs wafer </t>
-        </is>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B478" t="inlineStr">
-        <is>
-          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
-        </is>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B479" t="inlineStr">
-        <is>
-          <t>RER</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B480">
-        <v>1</v>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
+        </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
+          <t>RER</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B482" t="inlineStr">
-        <is>
-          <t>square meter</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B482">
+        <v>1</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>reference product</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: photovoltaic module assembly only, GaAs-Si tandem reference. Former reference product: photovoltaic module assembly only, GaAs-Si tandem reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED GaAs-Si MODULE ASSEMBLY COVERAGE, issue77,2026-10-18. Pallas et al.2020 DOI10.1007/s11367-020-01791-z, public SI S1,S4,S6: https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . SI S1 states that nanowire transfer is followed by both Si-cell and module manufacture. Existing installation already supplies1m2 complete Si cells plus1m2 GaAs ELO afterissue76, but contains no glass/encapsulant/frame/module assembly. Add one1m2 assembly-only reference using the published-source-compatible architecture of the existing ecoinvent3.10 RER single-Si panel-production inventory, copied into this workbook as a scoped engineering adaptation. Copy every original non-cell technosphere ingredient, processing service, packaging, factory and existing waste exchange plus biosphere flows; exclude the single photovoltaic-cell market input so no second Si cell or wafer is purchased. Preserve existing separate mounting/electricalinstallation/inverter purchases. Important geometry assumption: retain original GaAs design1m2 active Si cell per1m2 nominal module/0.28kWp; native panel reference cell coverage is0.9324100017547607m2 per modulem2. This uses its per-module-area assembly burden, not a claim that its original frame/layout is a measured GaAs module. Active-area packing, module gaps and optical fill factor require design validation; do not silently change28% module power or lifetime electricity denominator. Retain source reference module glass/EVA/backsheet/AlMg3 frame/interconnections and manufacture burdens rather than adding only an aluminium filler. No change to native PV panels or existing2026PV reference design. Copied waste outputs stay in the original reference scope; no new GaAs nanowire-specific EOL recovery, treatment route or substitution credit is invented. Background3.10 suppliers are migrated by existing supported-version import logic. Exact prospective tandem encapsulation, reliability, assembly yield and nanolayer disposal remain gaps, not asserted solved by a silicon-module analogue. Source native process includes some legacy disposal assumptions; these are retained once and documented, not additional external recycling credits.</t>
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B486" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E486" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F486" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G486" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H486" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I486" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
-        </is>
-      </c>
-      <c r="B487">
-        <v>1</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>square meter</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
-        </is>
-      </c>
-      <c r="I487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>market for 1-propanol</t>
-        </is>
-      </c>
-      <c r="B488">
-        <v>0.008138599805533886</v>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>1-propanol</t>
-        </is>
-      </c>
-      <c r="I488" t="inlineStr">
-        <is>
-          <t>1-propanol</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>market for acetone, liquid</t>
-        </is>
-      </c>
-      <c r="B489">
-        <v>0.01295899972319603</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>location</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>categories</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>type</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>acetone, liquid</t>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>comment</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>acetone, liquid</t>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>market for aluminium alloy, AlMg3</t>
+          <t xml:space="preserve">photovoltaic module production, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
       <c r="B490">
-        <v>2.6294000148773193</v>
+        <v>1</v>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>square meter</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>technosphere</t>
+          <t>production</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>aluminium alloy, AlMg3</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>aluminium alloy, AlMg3</t>
+          <t xml:space="preserve">photovoltaic module, gallium arsenide-silicon tandem, without cells</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>market for brazing solder, cadmium free</t>
+          <t>market for 1-propanol</t>
         </is>
       </c>
       <c r="B491">
-        <v>0.008764700032770634</v>
+        <v>0.008138599805533886</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
@@ -9279,27 +9210,27 @@
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>brazing solder, cadmium free</t>
+          <t>1-propanol</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>brazing solder, cadmium free</t>
+          <t>1-propanol</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>market for copper, cathode</t>
+          <t>market for acetone, liquid</t>
         </is>
       </c>
       <c r="B492">
-        <v>0.11269000172615051</v>
+        <v>0.01295899972319603</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
@@ -9314,27 +9245,27 @@
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t>acetone, liquid</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>copper, cathode</t>
+          <t>acetone, liquid</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>market for corrugated board box</t>
+          <t>market for aluminium alloy, AlMg3</t>
         </is>
       </c>
       <c r="B493">
-        <v>1.0956000089645386</v>
+        <v>2.6294000148773193</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -9349,32 +9280,32 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>corrugated board box</t>
+          <t>aluminium alloy, AlMg3</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
         <is>
-          <t>corrugated board box</t>
+          <t>aluminium alloy, AlMg3</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
+          <t>market for brazing solder, cadmium free</t>
         </is>
       </c>
       <c r="B494">
-        <v>4.710700035095215</v>
+        <v>0.008764700032770634</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>kilowatt hour</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -9384,23 +9315,23 @@
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>brazing solder, cadmium free</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>electricity, medium voltage</t>
+          <t>brazing solder, cadmium free</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>market for ethylvinylacetate, foil</t>
+          <t>market for copper, cathode</t>
         </is>
       </c>
       <c r="B495">
-        <v>1.0017000436782837</v>
+        <v>0.11269000172615051</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
@@ -9419,27 +9350,27 @@
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>ethylvinylacetate, foil</t>
+          <t>copper, cathode</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>ethylvinylacetate, foil</t>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>market for glass fibre reinforced plastic, polyamide, injection moulded</t>
+          <t>market for corrugated board box</t>
         </is>
       </c>
       <c r="B496">
-        <v>0.1878100037574768</v>
+        <v>1.0956000089645386</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -9454,23 +9385,23 @@
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyamide, injection moulded</t>
+          <t>corrugated board box</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>glass fibre reinforced plastic, polyamide, injection moulded</t>
+          <t>corrugated board box</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>market group for heat, district or industrial, natural gas</t>
+          <t>market group for electricity, medium voltage</t>
         </is>
       </c>
       <c r="B497">
-        <v>4.866390228271484</v>
+        <v>4.710700035095215</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
@@ -9479,7 +9410,7 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>megajoule</t>
+          <t>kilowatt hour</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -9489,27 +9420,27 @@
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>heat, district or industrial, natural gas</t>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>market for lubricating oil</t>
+          <t>market for ethylvinylacetate, foil</t>
         </is>
       </c>
       <c r="B498">
-        <v>0.0016069000121206045</v>
+        <v>1.0017000436782837</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -9524,27 +9455,27 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>lubricating oil</t>
+          <t>ethylvinylacetate, foil</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>lubricating oil</t>
+          <t>ethylvinylacetate, foil</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>market for methanol</t>
+          <t>market for glass fibre reinforced plastic, polyamide, injection moulded</t>
         </is>
       </c>
       <c r="B499">
-        <v>0.0021556001156568527</v>
+        <v>0.1878100037574768</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -9559,23 +9490,23 @@
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>methanol</t>
+          <t>glass fibre reinforced plastic, polyamide, injection moulded</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>methanol</t>
+          <t>glass fibre reinforced plastic, polyamide, injection moulded</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>market group for municipal solid waste</t>
+          <t>market group for heat, district or industrial, natural gas</t>
         </is>
       </c>
       <c r="B500">
-        <v>-0.029999999329447746</v>
+        <v>4.866390228271484</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
@@ -9584,7 +9515,7 @@
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>megajoule</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -9594,27 +9525,27 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>municipal solid waste</t>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>municipal solid waste</t>
+          <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>market for nickel, class 1</t>
+          <t>market for lubricating oil</t>
         </is>
       </c>
       <c r="B501">
-        <v>0.00016276999667752534</v>
+        <v>0.0016069000121206045</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
@@ -9629,32 +9560,32 @@
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t>lubricating oil</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>nickel, class 1</t>
+          <t>lubricating oil</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>market for photovoltaic panel factory</t>
+          <t>market for methanol</t>
         </is>
       </c>
       <c r="B502">
-        <v>3.999999989900971e-06</v>
+        <v>0.0021556001156568527</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -9664,27 +9595,27 @@
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>photovoltaic panel factory</t>
+          <t>methanol</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>photovoltaic panel factory</t>
+          <t>methanol</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>market for polyethylene terephthalate, granulate, amorphous</t>
+          <t>market group for municipal solid waste</t>
         </is>
       </c>
       <c r="B503">
-        <v>0.37297001481056213</v>
+        <v>-0.029999999329447746</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -9699,23 +9630,23 @@
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>polyethylene terephthalate, granulate, amorphous</t>
+          <t>municipal solid waste</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>polyethylene terephthalate, granulate, amorphous</t>
+          <t>municipal solid waste</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>market for polyvinylfluoride, film</t>
+          <t>market for nickel, class 1</t>
         </is>
       </c>
       <c r="B504">
-        <v>0.1103999987244606</v>
+        <v>0.00016276999667752534</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
@@ -9734,32 +9665,32 @@
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>polyvinylfluoride, film</t>
+          <t>nickel, class 1</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>polyvinylfluoride, film</t>
+          <t>nickel, class 1</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>market for silicone product</t>
+          <t>market for photovoltaic panel factory</t>
         </is>
       </c>
       <c r="B505">
-        <v>0.12195000052452087</v>
+        <v>3.999999989900971e-06</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -9769,23 +9700,23 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>silicone product</t>
+          <t>photovoltaic panel factory</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>silicone product</t>
+          <t>photovoltaic panel factory</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>market for solar glass, low-iron</t>
+          <t>market for polyethylene terephthalate, granulate, amorphous</t>
         </is>
       </c>
       <c r="B506">
-        <v>10.079000473022461</v>
+        <v>0.37297001481056213</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
@@ -9804,27 +9735,27 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>solar glass, low-iron</t>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>solar glass, low-iron</t>
+          <t>polyethylene terephthalate, granulate, amorphous</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>market group for tap water</t>
+          <t>market for polyvinylfluoride, film</t>
         </is>
       </c>
       <c r="B507">
-        <v>21.285999298095703</v>
+        <v>0.1103999987244606</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -9839,23 +9770,23 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>tap water</t>
+          <t>polyvinylfluoride, film</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>tap water</t>
+          <t>polyvinylfluoride, film</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>tempering, flat glass</t>
+          <t>market for silicone product</t>
         </is>
       </c>
       <c r="B508">
-        <v>10.079000473022461</v>
+        <v>0.12195000052452087</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
@@ -9874,23 +9805,23 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>tempering, flat glass</t>
+          <t>silicone product</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>tempering, flat glass</t>
+          <t>silicone product</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>market for vinyl acetate</t>
+          <t>market for solar glass, low-iron</t>
         </is>
       </c>
       <c r="B509">
-        <v>0.0016434000572189689</v>
+        <v>10.079000473022461</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
@@ -9909,27 +9840,27 @@
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>vinyl acetate</t>
+          <t>solar glass, low-iron</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>vinyl acetate</t>
+          <t>solar glass, low-iron</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>market for waste mineral oil</t>
+          <t>market group for tap water</t>
         </is>
       </c>
       <c r="B510">
-        <v>-0.0015680805081501603</v>
+        <v>21.285999298095703</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -9944,27 +9875,27 @@
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>waste mineral oil</t>
+          <t>tap water</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>waste mineral oil</t>
+          <t>tap water</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>market for waste mineral oil</t>
+          <t>tempering, flat glass</t>
         </is>
       </c>
       <c r="B511">
-        <v>-3.8819438486825675e-05</v>
+        <v>10.079000473022461</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -9979,27 +9910,27 @@
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>waste mineral oil</t>
+          <t>tempering, flat glass</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
         <is>
-          <t>waste mineral oil</t>
+          <t>tempering, flat glass</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>market group for waste plastic, mixture</t>
+          <t>market for vinyl acetate</t>
         </is>
       </c>
       <c r="B512">
-        <v>-1.6861000061035156</v>
+        <v>0.0016434000572189689</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>GLO</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -10014,27 +9945,27 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>waste plastic, mixture</t>
+          <t>vinyl acetate</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>waste plastic, mixture</t>
+          <t>vinyl acetate</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>market for waste polyvinylfluoride</t>
+          <t>market for waste mineral oil</t>
         </is>
       </c>
       <c r="B513">
-        <v>-0.1103999987244606</v>
+        <v>-0.0015680805081501603</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>Europe without Switzerland</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -10049,32 +9980,32 @@
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>waste polyvinylfluoride</t>
+          <t>waste mineral oil</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
         <is>
-          <t>waste polyvinylfluoride</t>
+          <t>waste mineral oil</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
+          <t>market for waste mineral oil</t>
         </is>
       </c>
       <c r="B514">
-        <v>-0.020764166489243507</v>
+        <v>-3.8819438486825675e-05</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Europe without Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -10084,32 +10015,32 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>waste mineral oil</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>waste mineral oil</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
+          <t>market group for waste plastic, mixture</t>
         </is>
       </c>
       <c r="B515">
-        <v>-0.0005218342412263155</v>
+        <v>-1.6861000061035156</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>RER</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>cubic meter</t>
+          <t>kilogram</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -10119,27 +10050,27 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>waste plastic, mixture</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>wastewater, average</t>
+          <t>waste plastic, mixture</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>wire drawing, copper</t>
+          <t>market for waste polyvinylfluoride</t>
         </is>
       </c>
       <c r="B516">
-        <v>0.11269000172615051</v>
+        <v>-0.1103999987244606</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>RER</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -10154,2301 +10085,2490 @@
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>wire drawing, copper</t>
+          <t>waste polyvinylfluoride</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
         <is>
-          <t>wire drawing, copper</t>
+          <t>waste polyvinylfluoride</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>market for wastewater, average</t>
         </is>
       </c>
       <c r="B517">
-        <v>0.0031928999815136194</v>
+        <v>-0.020764166489243507</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Europe without Switzerland</t>
+        </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
           <t>cubic meter</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>air</t>
-        </is>
-      </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t/>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B518">
+        <v>-0.0005218342412263155</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+      <c r="B519">
+        <v>0.11269000172615051</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>wire drawing, copper</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B520" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
-        </is>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B521" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B522">
-        <v>1</v>
+          <t>Water</t>
+        </is>
+      </c>
+      <c r="B520">
+        <v>0.0031928999815136194</v>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>air</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>reference product</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t xml:space="preserve">hydrogen bromide</t>
+          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B525" t="inlineStr">
-        <is>
-          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
-        </is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B525">
+        <v>1</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen bromide</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B526" t="inlineStr">
+      <c r="B529" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen bromide, elemental synthesis engineering reference. Former reference product: hydrogen bromide, elemental synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B528" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E528" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H528" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I528" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
-        </is>
-      </c>
-      <c r="B529">
-        <v>1</v>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide</t>
-        </is>
-      </c>
-      <c r="I529" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide</t>
-        </is>
-      </c>
-    </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>market for hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-      <c r="B530">
-        <v>0.012457979038955904</v>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F530" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G530" t="inlineStr">
-        <is>
-          <t>hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-      <c r="I530" t="inlineStr">
-        <is>
-          <t>hydrogen, gaseous, low pressure</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>market for bromine</t>
-        </is>
-      </c>
-      <c r="B531">
-        <v>0.9875420209610442</v>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F531" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G531" t="inlineStr">
-        <is>
-          <t>bromine</t>
-        </is>
-      </c>
-      <c r="I531" t="inlineStr">
-        <is>
-          <t>bromine</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B532">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
+        </is>
+      </c>
+      <c r="B533">
+        <v>1</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F532" t="inlineStr">
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen bromide</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen bromide</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>market for hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="B534">
+        <v>0.012457979038955904</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I532" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
+          <t>market for bromine</t>
+        </is>
+      </c>
+      <c r="B535">
+        <v>0.9875420209610442</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>bromine</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>bromine</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B536">
+        <v>1</v>
+      </c>
+      <c r="C536" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B537">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide</t>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>kilogram</t>
+          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>location</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+          <t>GLO</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B541">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen iodide</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B541" t="inlineStr">
+      <c r="B545" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: hydrogen iodide, elemental synthesis engineering reference. Former reference product: hydrogen iodide, elemental synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B543" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H543" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
-        </is>
-      </c>
-      <c r="B544">
-        <v>1</v>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F544" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G544" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide</t>
-        </is>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>market for hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-      <c r="B545">
-        <v>0.007880388831518929</v>
-      </c>
-      <c r="C545" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F545" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G545" t="inlineStr">
-        <is>
-          <t>hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-      <c r="I545" t="inlineStr">
-        <is>
-          <t>hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-    </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>market for iodine</t>
-        </is>
-      </c>
-      <c r="B546">
-        <v>0.9921196111684811</v>
-      </c>
-      <c r="C546" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F546" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G546" t="inlineStr">
-        <is>
-          <t>iodine</t>
-        </is>
-      </c>
-      <c r="I546" t="inlineStr">
-        <is>
-          <t>iodine</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B547">
-        <v>1</v>
-      </c>
-      <c r="C547" t="inlineStr">
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
+        </is>
+      </c>
+      <c r="B549">
+        <v>1</v>
+      </c>
+      <c r="C549" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen iodide</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen iodide</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
+          <t>market for hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="B550">
+        <v>0.007880388831518929</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B551" t="inlineStr">
+          <t>market for iodine</t>
+        </is>
+      </c>
+      <c r="B551">
+        <v>0.9921196111684811</v>
+      </c>
+      <c r="C551" t="inlineStr">
         <is>
           <t>GLO</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>iodine</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market group for electricity, medium voltage</t>
         </is>
       </c>
       <c r="B552">
         <v>1</v>
       </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide</t>
-        </is>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B554" t="inlineStr">
-        <is>
-          <t>kilogram</t>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B557">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl bromide</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B556" t="inlineStr">
+      <c r="B561" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: ethyl bromide, ethanol route engineering reference. Former reference product: ethyl bromide, ethanol route engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H558" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
-        </is>
-      </c>
-      <c r="B559">
-        <v>1</v>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide</t>
-        </is>
-      </c>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>market for ethanol, without water, in 99.7% solution state, from ethylene</t>
-        </is>
-      </c>
-      <c r="B560">
-        <v>0.422783253491915</v>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
-        </is>
-      </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
-        </is>
-      </c>
-      <c r="B561">
-        <v>0.742543545693152</v>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F561" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide</t>
-        </is>
-      </c>
-      <c r="I561" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen bromide</t>
-        </is>
-      </c>
-    </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>market for wastewater, average</t>
-        </is>
-      </c>
-      <c r="B562">
-        <v>-0.0001653267991850669</v>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>cubic meter</t>
-        </is>
-      </c>
-      <c r="F562" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>wastewater, average</t>
-        </is>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>wastewater, average</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B563">
-        <v>0.5</v>
-      </c>
-      <c r="C563" t="inlineStr">
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
+        </is>
+      </c>
+      <c r="B565">
+        <v>1</v>
+      </c>
+      <c r="C565" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I563" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl bromide</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
+          <t>market for ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="B566">
+        <v>0.422783253491915</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
         </is>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
+          <t xml:space="preserve">hydrogen bromide production, direct synthesis</t>
+        </is>
+      </c>
+      <c r="B567">
+        <v>0.742543545693152</v>
+      </c>
+      <c r="C567" t="inlineStr">
         <is>
           <t>GLO</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen bromide</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen bromide</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t>market for wastewater, average</t>
         </is>
       </c>
       <c r="B568">
-        <v>1</v>
+        <v>-0.0001653267991850669</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B569">
+        <v>0.5</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B574">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl iodide</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B572" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: ethyl iodide, ethanol route engineering reference. Former reference product: ethyl iodide, ethanol route engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B574" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C574" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D574" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E574" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F574" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G574" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H574" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I574" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
-        </is>
-      </c>
-      <c r="B575">
-        <v>1</v>
-      </c>
-      <c r="C575" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D575" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F575" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G575" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide</t>
-        </is>
-      </c>
-      <c r="I575" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide</t>
-        </is>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>market for ethanol, without water, in 99.7% solution state, from ethylene</t>
-        </is>
-      </c>
-      <c r="B576">
-        <v>0.2953775898114511</v>
-      </c>
-      <c r="C576" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D576" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F576" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G576" t="inlineStr">
-        <is>
-          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
-        </is>
-      </c>
-      <c r="I576" t="inlineStr">
-        <is>
-          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
-        </is>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
-        </is>
-      </c>
-      <c r="B577">
-        <v>0.820128005718152</v>
-      </c>
-      <c r="C577" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D577" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F577" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide</t>
-        </is>
-      </c>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hydrogen iodide</t>
-        </is>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>market for wastewater, average</t>
-        </is>
-      </c>
-      <c r="B578">
-        <v>-0.00011550559552960325</v>
-      </c>
-      <c r="C578" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D578" t="inlineStr">
-        <is>
-          <t>cubic meter</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>wastewater, average</t>
-        </is>
-      </c>
-      <c r="I578" t="inlineStr">
-        <is>
-          <t>wastewater, average</t>
-        </is>
-      </c>
-    </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B579">
-        <v>0.5</v>
-      </c>
-      <c r="C579" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D579" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F579" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G579" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I579" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Exchanges</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B582" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide production, for catalysts</t>
+          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
+        </is>
+      </c>
+      <c r="B582">
+        <v>1</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl iodide</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B583" t="inlineStr">
-        <is>
-          <t>GLO</t>
+          <t>market for ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="B583">
+        <v>0.2953775898114511</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>ethanol, without water, in 99.7% solution state, from ethylene</t>
         </is>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t xml:space="preserve">hydrogen iodide production, direct synthesis</t>
         </is>
       </c>
       <c r="B584">
-        <v>1</v>
+        <v>0.820128005718152</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen iodide</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hydrogen iodide</t>
+        </is>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B585" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide, for catalysts</t>
+          <t>market for wastewater, average</t>
+        </is>
+      </c>
+      <c r="B585">
+        <v>-0.00011550559552960325</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>wastewater, average</t>
         </is>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B586">
+        <v>0.5</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copper iodide production, for catalysts</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B586" t="inlineStr">
+      <c r="B593" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
     </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
+    <row r="594">
+      <c r="A594" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B587" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
         </is>
       </c>
     </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
+    <row r="595">
+      <c r="A595" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B588" t="inlineStr">
+      <c r="B595" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: copper iodide, catalyst engineering reference. Former reference product: copper iodide, catalyst engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B590" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C590" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D590" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E590" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F590" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H590" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I590" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide production, for catalysts</t>
-        </is>
-      </c>
-      <c r="B591">
-        <v>1</v>
-      </c>
-      <c r="C591" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D591" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F591" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G591" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide, for catalysts</t>
-        </is>
-      </c>
-      <c r="I591" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide, for catalysts</t>
-        </is>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>market for copper, cathode</t>
-        </is>
-      </c>
-      <c r="B592">
-        <v>0.33366155515394635</v>
-      </c>
-      <c r="C592" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D592" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F592" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G592" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-      <c r="I592" t="inlineStr">
-        <is>
-          <t>copper, cathode</t>
-        </is>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>market for iodine</t>
-        </is>
-      </c>
-      <c r="B593">
-        <v>0.6663384448460538</v>
-      </c>
-      <c r="C593" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D593" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F593" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G593" t="inlineStr">
-        <is>
-          <t>iodine</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>iodine</t>
-        </is>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B594">
-        <v>1</v>
-      </c>
-      <c r="C594" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D594" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F594" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G594" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B597" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B598" t="inlineStr">
-        <is>
-          <t>GLO</t>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t xml:space="preserve">copper iodide production, for catalysts</t>
         </is>
       </c>
       <c r="B599">
         <v>1</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
+        </is>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B600" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diethylzinc</t>
+          <t>market for copper, cathode</t>
+        </is>
+      </c>
+      <c r="B600">
+        <v>0.33366155515394635</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>copper, cathode</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B601" t="inlineStr">
+          <t>market for iodine</t>
+        </is>
+      </c>
+      <c r="B601">
+        <v>0.6663384448460538</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
         <is>
           <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>iodine</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>iodine</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B602">
+        <v>1</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B607">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diethylzinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B602" t="inlineStr">
+      <c r="B610" t="inlineStr">
         <is>
           <t>Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en .</t>
         </is>
       </c>
     </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
+    <row r="611">
+      <c r="A611" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B603" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: diethylzinc, organozinc synthesis engineering reference. Former reference product: diethylzinc, organozinc synthesis engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED DIETHYLZINC IDENTITY AND Zn FEED, issue83,2026-10-18. Pallas2020 SI S4 identifies diethylzinc8.5e-6kg/m2 MOVPE. CN100408584C Example1:600gZn,250mLEtI,250mLEtBr,10gCuI; reported trialyieldabout85%,not a measured semiconductorplant inventory. https://patents.google.com/patent/CN100408584C/en . Replace onlyMOVPEgenericorganicchemical8.5mg/m2 by the same mass of an explicitZn(C2H5)2 reference; retainedZn fraction=0.529375566783262. Do not add elementalZn on top of a complete DEZ supplier. Use the patentdirectZn/ethylhalide route as a namedengineeringvariant,not a claim of the actualPallas chemicalvendor. Convert250mL eachEtBr/EtI with explicitlyassumed20C densities1.46/1.94kg/L;sourcebatch0.365kgEtBr+0.485kgEtI+0.600kgZn+0.010kgCuI. IsolatednewDEZ=0.3390440898698082kg perbatch at85% of halide-limitedtheoreticalyield; patent doesnot report that exactkgoutput or allresiduefates.30gDEZinitiator is treatedasclosedcirculatingseed,not counted bothasnewoutput andnewfreshinput;initialseedstock/startup-loss allocation is a gap.95%versus85%yield sensitivity mustnot silentlychangeoldper-m2dosage. Use1kWh/kg productmanufacture as explicitheating,distillation/coolingallowance,plus0.05kgN2/kgproduct and0.01kgH2/kgproduct purge references;actualpurityupgrade,powderactivation,purgeflow,leaks andutilities remainunmeasured. NativeZnmarket is a bulkrefinedsupplyproxy,not certified6Npowder;semiconductor-gradepurification gap remains. No assumedclosedloopZn-saltorCuIrecovery; matchall grossZn/ethylhalide/CuImass notretainedin1kg producttoexistingmixedhazardouswasteprovider with no metalcredit. MixedresiduecontainsZn/halides/Cu andunreactedmaterial;separateelementfates areunresolved. Buildmissingethylhalides via balancedEtOH+HX-&gt;EtX+H2O precursorreferences,withHX fromH2+halogen andCuIfromCu+I;these are explicit100%stoichiometric precursorconversionreferences,not measuredindustrialyields. Their1kWh/kgHX/CuI and0.5kWh/kgEtX processingallowances andwastewaterwateroutflow are engineeringproxies. Testprecursoryields90-100%;do not claim industrialrecipe closure because elementalbalances close. UsepetrochemicalethanolRER,realBr/I/Cu/H2feeds,not genericorganicchemical as missingZn substitute. Preserve sourceoperatingnanowirearea afterissue76 andallotherMOVPEinputs. Highpuritymetal,saltrecycling,pyrophoricreagent losses andactualcarrier-solvent grade requirefuturedata. No native,runtime,YAML or primary-secondaryshare edits.</t>
         </is>
       </c>
     </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B605" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D605" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E605" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F605" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G605" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H605" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I605" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
-        </is>
-      </c>
-      <c r="B606">
-        <v>1</v>
-      </c>
-      <c r="C606" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D606" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F606" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G606" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diethylzinc</t>
-        </is>
-      </c>
-      <c r="I606" t="inlineStr">
-        <is>
-          <t xml:space="preserve">diethylzinc</t>
-        </is>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>market for zinc</t>
-        </is>
-      </c>
-      <c r="B607">
-        <v>1.7696813421239639</v>
-      </c>
-      <c r="C607" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D607" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F607" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
-      </c>
-      <c r="I607" t="inlineStr">
-        <is>
-          <t>zinc</t>
-        </is>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
-        </is>
-      </c>
-      <c r="B608">
-        <v>1.076556149792078</v>
-      </c>
-      <c r="C608" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D608" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F608" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G608" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide</t>
-        </is>
-      </c>
-      <c r="I608" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl bromide</t>
-        </is>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
-        </is>
-      </c>
-      <c r="B609">
-        <v>1.4304924182168708</v>
-      </c>
-      <c r="C609" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D609" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F609" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G609" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide</t>
-        </is>
-      </c>
-      <c r="I609" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ethyl iodide</t>
-        </is>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide production, for catalysts</t>
-        </is>
-      </c>
-      <c r="B610">
-        <v>0.029494689035399396</v>
-      </c>
-      <c r="C610" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D610" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F610" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G610" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide, for catalysts</t>
-        </is>
-      </c>
-      <c r="I610" t="inlineStr">
-        <is>
-          <t xml:space="preserve">copper iodide, for catalysts</t>
-        </is>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>market for hazardous waste, for incineration</t>
-        </is>
-      </c>
-      <c r="B611">
-        <v>-3.3062245991683117</v>
-      </c>
-      <c r="C611" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D611" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F611" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G611" t="inlineStr">
-        <is>
-          <t>hazardous waste, for incineration</t>
-        </is>
-      </c>
-      <c r="I611" t="inlineStr">
-        <is>
-          <t>hazardous waste, for incineration</t>
-        </is>
-      </c>
-    </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>market for nitrogen, liquid</t>
-        </is>
-      </c>
-      <c r="B612">
-        <v>0.05</v>
-      </c>
-      <c r="C612" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D612" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F612" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G612" t="inlineStr">
-        <is>
-          <t>nitrogen, liquid</t>
-        </is>
-      </c>
-      <c r="I612" t="inlineStr">
-        <is>
-          <t>nitrogen, liquid</t>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>market for hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-      <c r="B613">
-        <v>0.01</v>
-      </c>
-      <c r="C613" t="inlineStr">
-        <is>
-          <t>RER</t>
-        </is>
-      </c>
-      <c r="D613" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F613" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G613" t="inlineStr">
-        <is>
-          <t>hydrogen, gaseous, low pressure</t>
-        </is>
-      </c>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>hydrogen, gaseous, low pressure</t>
+          <t>Exchanges</t>
         </is>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>market group for electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="B614">
-        <v>1</v>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
       </c>
       <c r="C614" t="inlineStr">
         <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>product</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diethylzinc production, organozinc synthesis</t>
+        </is>
+      </c>
+      <c r="B615">
+        <v>1</v>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D614" t="inlineStr">
-        <is>
-          <t>kilowatt hour</t>
-        </is>
-      </c>
-      <c r="F614" t="inlineStr">
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diethylzinc</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diethylzinc</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>market for zinc</t>
+        </is>
+      </c>
+      <c r="B616">
+        <v>1.7696813421239639</v>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G614" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
-        </is>
-      </c>
-      <c r="I614" t="inlineStr">
-        <is>
-          <t>electricity, medium voltage</t>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>zinc</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>zinc</t>
         </is>
       </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B617" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
+          <t xml:space="preserve">ethyl bromide production, from ethanol</t>
+        </is>
+      </c>
+      <c r="B617">
+        <v>1.076556149792078</v>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl bromide</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl bromide</t>
         </is>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="B618" t="inlineStr">
+          <t xml:space="preserve">ethyl iodide production, from ethanol</t>
+        </is>
+      </c>
+      <c r="B618">
+        <v>1.4304924182168708</v>
+      </c>
+      <c r="C618" t="inlineStr">
         <is>
           <t>GLO</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl iodide</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ethyl iodide</t>
         </is>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>production amount</t>
+          <t xml:space="preserve">copper iodide production, for catalysts</t>
         </is>
       </c>
       <c r="B619">
-        <v>1</v>
+        <v>0.029494689035399396</v>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t xml:space="preserve">copper iodide, for catalysts</t>
+        </is>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="B620" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arsenic, high purity, from arsine</t>
+          <t>market for hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="B620">
+        <v>-3.3062245991683117</v>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>hazardous waste, for incineration</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B621" t="inlineStr">
+          <t>market for nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="B621">
+        <v>0.05</v>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
         <is>
           <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>nitrogen, liquid</t>
         </is>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B622" t="inlineStr">
-        <is>
-          <t>Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+          <t>market for hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="B622">
+        <v>0.01</v>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>RER</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>hydrogen, gaseous, low pressure</t>
         </is>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
+          <t>market group for electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="B623">
+        <v>1</v>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>kilowatt hour</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>electricity, medium voltage</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B628">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx .</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B623" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: arsine-to-arsenic purification, source-yield engineering reference. Former reference product: arsine-to-arsenic purification, source-yield engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
         </is>
       </c>
     </row>
-    <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>Exchanges</t>
-        </is>
-      </c>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B625" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="C625" t="inlineStr">
-        <is>
-          <t>location</t>
-        </is>
-      </c>
-      <c r="D625" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="E625" t="inlineStr">
-        <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="F625" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="G625" t="inlineStr">
-        <is>
-          <t>reference product</t>
-        </is>
-      </c>
-      <c r="H625" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="I625" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
-        </is>
-      </c>
-      <c r="B626">
-        <v>1</v>
-      </c>
-      <c r="C626" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D626" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F626" t="inlineStr">
-        <is>
-          <t>production</t>
-        </is>
-      </c>
-      <c r="G626" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arsenic, high purity, from arsine</t>
-        </is>
-      </c>
-      <c r="I626" t="inlineStr">
-        <is>
-          <t xml:space="preserve">arsenic, high purity, from arsine</t>
-        </is>
-      </c>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>arsine production</t>
-        </is>
-      </c>
-      <c r="B627">
-        <v>1.5299443671611501</v>
-      </c>
-      <c r="C627" t="inlineStr">
-        <is>
-          <t>GLO</t>
-        </is>
-      </c>
-      <c r="D627" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F627" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G627" t="inlineStr">
-        <is>
-          <t>arsine</t>
-        </is>
-      </c>
-      <c r="I627" t="inlineStr">
-        <is>
-          <t>arsine</t>
-        </is>
-      </c>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>treatment of hazardous waste, underground deposit</t>
-        </is>
-      </c>
-      <c r="B628">
-        <v>-0.4705881999999999</v>
-      </c>
-      <c r="C628" t="inlineStr">
-        <is>
-          <t>RoW</t>
-        </is>
-      </c>
-      <c r="D628" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="F628" t="inlineStr">
-        <is>
-          <t>technosphere</t>
-        </is>
-      </c>
-      <c r="G628" t="inlineStr">
-        <is>
-          <t>hazardous waste, for underground deposit</t>
-        </is>
-      </c>
-      <c r="I628" t="inlineStr">
-        <is>
-          <t>hazardous waste, for underground deposit</t>
-        </is>
-      </c>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>Hydrogen</t>
-        </is>
-      </c>
-      <c r="B629">
-        <v>0.05935616716115022</v>
-      </c>
-      <c r="D629" t="inlineStr">
-        <is>
-          <t>kilogram</t>
-        </is>
-      </c>
-      <c r="E629" t="inlineStr">
-        <is>
-          <t>air::non-urban air or from high stacks</t>
-        </is>
-      </c>
-      <c r="F629" t="inlineStr">
-        <is>
-          <t>biosphere</t>
-        </is>
-      </c>
-      <c r="H629" t="inlineStr">
-        <is>
-          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="B632" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boron trichloride production, carbochlorination</t>
-        </is>
-      </c>
-    </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>location</t>
+          <t xml:space="preserve">type</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>GLO</t>
+          <t xml:space="preserve">processwithreferenceproduct</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>production amount</t>
-        </is>
-      </c>
-      <c r="B634">
-        <v>1</v>
+          <t>Exchanges</t>
+        </is>
       </c>
     </row>
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>categories</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B635" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boron trichloride</t>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>product</t>
         </is>
       </c>
     </row>
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="B636" t="inlineStr">
+          <t xml:space="preserve">arsenic production, high purity, from arsine</t>
+        </is>
+      </c>
+      <c r="B636">
+        <v>1</v>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
         <is>
           <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>production</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t xml:space="preserve">arsenic, high purity, from arsine</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="B637" t="inlineStr">
-        <is>
-          <t>Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en .</t>
+          <t>arsine production</t>
+        </is>
+      </c>
+      <c r="B637">
+        <v>1.5299443671611501</v>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>arsine</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>arsine</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
+          <t>treatment of hazardous waste, underground deposit</t>
+        </is>
+      </c>
+      <c r="B638">
+        <v>-0.4705881999999999</v>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>RoW</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>technosphere</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>hazardous waste, for underground deposit</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Hydrogen</t>
+        </is>
+      </c>
+      <c r="B639">
+        <v>0.05935616716115022</v>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>air::non-urban air or from high stacks</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>biosphere</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>APPROVED ARSENIC-EQUIVALENT ARSINE FEED, issue111,2026-10-18. Pallas et al.2020, DOI10.1007/s11367-020-01791-z, SI S6. https://media.springernature.com/full/springer-static/esm/art%3A10.1007%2Fs11367-020-01791-z/MediaObjects/11367_2020_1791_MOESM1_ESM.docx . Source explicitly specifies1.4705882kg elemental2N arsenic and calls for about1.53kgAsH3 when using arsineproduction as proxy. Current workbook copied1.4705882kg without compoundconversion. Use atomicmasses As74.921595,H1.008:Asfraction=0.9612037088176696 andarsinefeed=1.5299443671611501kg per1kg7NAs. Preserve source elementalfeed and impliedpurificationretention1/1.4705882~68%;do not accidentallytreatcompoundreplacement as100%Asrecovery. Add explicit netAsH3-&gt;As+1.5H2 conversion:elementalAsreject=0.4705881999999999kg toexisting hazardousunderground-disposalproxy,hydrogenreleasedfromfeed=0.05935616716115022kg biosphereair. This is a chemicallydefined engineeringconversion/fate,not validatedindustrialarsine-based7Nrefining. Sourcepreferenceisoriginalmetallic2NAs purification;actualhighpurityfeedrouteandpurificationutilitiesrequireoriginalSmith2018 processdata. Keep8.1176471kWh andoriginalexternalH2.0941176kg,Ar.0470588kg as existingpurification/purge allowances;theirrecycle/ventfates areunresolved,notclaimedatomclosedfornonreactivepurge. Do not subtractgeneratedH2 fromexternalpurge orcredit hydrogenmarket without evidencedcapturequality. AddedAsreject isnotanextra retainedproduct orrecyclingcredit. No change7NAs1kgoutput,GaAs boulecomposition,downstreamyield,nanowireAsH3dose,lifetime/substratereuse orprimary/secondaryshares. SourceAsfraction.961rounds to1.53kg;exactmolarconversionusedratherthanrounded1.53. Existingworkbookonly,no runtime/native edits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boron trichloride production, carbochlorination</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>GLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>production amount</t>
+        </is>
+      </c>
+      <c r="B644">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>reference product</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">boron trichloride</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>kilogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en .</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B638" t="inlineStr">
+      <c r="B648" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: boron trichloride, carbochlorination engineering reference. Former reference product: boron trichloride, carbochlorination engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
@@ -12458,295 +12578,307 @@
         </is>
       </c>
     </row>
-    <row r="639">
-      <c r="A639" t="inlineStr">
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="640">
-      <c r="A640" t="inlineStr">
+    <row r="651">
+      <c r="A651" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B640" t="inlineStr">
+      <c r="B651" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C640" t="inlineStr">
+      <c r="C651" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D640" t="inlineStr">
+      <c r="D651" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E640" t="inlineStr">
+      <c r="E651" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F640" t="inlineStr">
+      <c r="F651" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G640" t="inlineStr">
+      <c r="G651" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H640" t="inlineStr">
+      <c r="H651" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I640" t="inlineStr">
+      <c r="I651" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="641">
-      <c r="A641" t="inlineStr">
+    <row r="652">
+      <c r="A652" t="inlineStr">
         <is>
           <t xml:space="preserve">boron trichloride production, carbochlorination</t>
         </is>
       </c>
-      <c r="B641">
-        <v>1</v>
-      </c>
-      <c r="C641" t="inlineStr">
+      <c r="B652">
+        <v>1</v>
+      </c>
+      <c r="C652" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D641" t="inlineStr">
+      <c r="D652" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F641" t="inlineStr">
+      <c r="F652" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="G641" t="inlineStr">
+      <c r="G652" t="inlineStr">
         <is>
           <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
-      <c r="I641" t="inlineStr">
+      <c r="I652" t="inlineStr">
         <is>
           <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
     </row>
-    <row r="642">
-      <c r="A642" t="inlineStr">
+    <row r="653">
+      <c r="A653" t="inlineStr">
         <is>
           <t>boric oxide production</t>
         </is>
       </c>
-      <c r="B642">
+      <c r="B653">
         <v>0.29710225332878115</v>
       </c>
-      <c r="C642" t="inlineStr">
+      <c r="C653" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D642" t="inlineStr">
+      <c r="D653" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F642" t="inlineStr">
+      <c r="F653" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G642" t="inlineStr">
+      <c r="G653" t="inlineStr">
         <is>
           <t>boric oxide</t>
         </is>
       </c>
-      <c r="I642" t="inlineStr">
+      <c r="I653" t="inlineStr">
         <is>
           <t>boric oxide</t>
         </is>
       </c>
     </row>
-    <row r="643">
-      <c r="A643" t="inlineStr">
+    <row r="654">
+      <c r="A654" t="inlineStr">
         <is>
           <t>market for graphite</t>
         </is>
       </c>
-      <c r="B643">
+      <c r="B654">
         <v>0.15377688630932057</v>
       </c>
-      <c r="C643" t="inlineStr">
+      <c r="C654" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D643" t="inlineStr">
+      <c r="D654" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F643" t="inlineStr">
+      <c r="F654" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G643" t="inlineStr">
+      <c r="G654" t="inlineStr">
         <is>
           <t>graphite</t>
         </is>
       </c>
-      <c r="I643" t="inlineStr">
+      <c r="I654" t="inlineStr">
         <is>
           <t>graphite</t>
         </is>
       </c>
     </row>
-    <row r="644">
-      <c r="A644" t="inlineStr">
+    <row r="655">
+      <c r="A655" t="inlineStr">
         <is>
           <t>market for chlorine, liquid</t>
         </is>
       </c>
-      <c r="B644">
+      <c r="B655">
         <v>0.9077330146807784</v>
       </c>
-      <c r="C644" t="inlineStr">
+      <c r="C655" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D644" t="inlineStr">
+      <c r="D655" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F644" t="inlineStr">
+      <c r="F655" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G644" t="inlineStr">
+      <c r="G655" t="inlineStr">
         <is>
           <t>chlorine, liquid</t>
         </is>
       </c>
-      <c r="I644" t="inlineStr">
+      <c r="I655" t="inlineStr">
         <is>
           <t>chlorine, liquid</t>
         </is>
       </c>
     </row>
-    <row r="645">
-      <c r="A645" t="inlineStr">
+    <row r="656">
+      <c r="A656" t="inlineStr">
         <is>
           <t>market group for electricity, medium voltage</t>
         </is>
       </c>
-      <c r="B645">
-        <v>1</v>
-      </c>
-      <c r="C645" t="inlineStr">
+      <c r="B656">
+        <v>1</v>
+      </c>
+      <c r="C656" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D645" t="inlineStr">
+      <c r="D656" t="inlineStr">
         <is>
           <t>kilowatt hour</t>
         </is>
       </c>
-      <c r="F645" t="inlineStr">
+      <c r="F656" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G645" t="inlineStr">
+      <c r="G656" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>
       </c>
-      <c r="I645" t="inlineStr">
+      <c r="I656" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
-    <row r="646">
-      <c r="A646" t="inlineStr">
+    <row r="657">
+      <c r="A657" t="inlineStr">
         <is>
           <t>market for heat, district or industrial, natural gas</t>
         </is>
       </c>
-      <c r="B646">
+      <c r="B657">
         <v>3</v>
       </c>
-      <c r="C646" t="inlineStr">
+      <c r="C657" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D646" t="inlineStr">
+      <c r="D657" t="inlineStr">
         <is>
           <t>megajoule</t>
         </is>
       </c>
-      <c r="F646" t="inlineStr">
+      <c r="F657" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G646" t="inlineStr">
+      <c r="G657" t="inlineStr">
         <is>
           <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
-      <c r="I646" t="inlineStr">
+      <c r="I657" t="inlineStr">
         <is>
           <t>heat, district or industrial, natural gas</t>
         </is>
       </c>
     </row>
-    <row r="647">
-      <c r="A647" t="inlineStr">
+    <row r="658">
+      <c r="A658" t="inlineStr">
         <is>
           <t>Carbon monoxide, fossil</t>
         </is>
       </c>
-      <c r="B647">
+      <c r="B658">
         <v>0.35861215431888016</v>
       </c>
-      <c r="D647" t="inlineStr">
+      <c r="D658" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="E647" t="inlineStr">
+      <c r="E658" t="inlineStr">
         <is>
           <t>air::non-urban air or from high stacks</t>
         </is>
       </c>
-      <c r="F647" t="inlineStr">
+      <c r="F658" t="inlineStr">
         <is>
           <t>biosphere</t>
         </is>
       </c>
-      <c r="H647" t="inlineStr">
+      <c r="H658" t="inlineStr">
         <is>
           <t>APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
  CVDreference50%boronprecursordepositionutilization and95%finishedsolidretention,notindustrialmeasurements;NH3:BCl3molarratio4frompatentexample. Grossprecursorfeedper1grossBN:2BCl3+8NH3. OneBCl3 reactswithoneNH3 -&gt;BN+3HCl;otherBCl3 hydrolyzeswith3H2O -&gt;H3BO3+3HCl. SixremainingNH3 neutralizes6HCl -&gt;6NH4Cl;oneextraNH3 isneutralizedwith.5H2SO4 -&gt;.5(NH4)2SO4. Net2BCl3+8NH3+3H2O+.5H2SO4 -&gt;BN+H3BO3+6NH4Cl+.5(NH4)2SO4. Atomandmassbalanced;Bdeposited50%,finishedBN95%ofdepositedsolid. AllunretainedB/N/Clcapturedaswetbrineis100%collectionREFERENCE,notmeasuredabatementefficiency;actualfugitiveNH3/HClrequiresdata. Testboronutilization10-90%,retention90-100%,gasratio2-5 andcapture95-100%withrecalculatedchemistry/fates,notindependentquantitymultipliers.
@@ -12755,83 +12887,83 @@
         </is>
       </c>
     </row>
-    <row r="650">
-      <c r="A650" t="inlineStr">
+    <row r="661">
+      <c r="A661" t="inlineStr">
         <is>
           <t>Activity</t>
         </is>
       </c>
-      <c r="B650" t="inlineStr">
+      <c r="B661" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
     </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
+    <row r="662">
+      <c r="A662" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="B651" t="inlineStr">
+      <c r="B662" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
     </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
+    <row r="663">
+      <c r="A663" t="inlineStr">
         <is>
           <t>production amount</t>
         </is>
       </c>
-      <c r="B652">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
+      <c r="B663">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="B653" t="inlineStr">
+      <c r="B664" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
     </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
+    <row r="665">
+      <c r="A665" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B654" t="inlineStr">
+      <c r="B665" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
     </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
+    <row r="666">
+      <c r="A666" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="B655" t="inlineStr">
+      <c r="B666" t="inlineStr">
         <is>
           <t>Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en .</t>
         </is>
       </c>
     </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
+    <row r="667">
+      <c r="A667" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="B656" t="inlineStr">
+      <c r="B667" t="inlineStr">
         <is>
           <t xml:space="preserve">Nomenclature revision, 2026-10-19. Former activity name: pyrolytic boron nitride crucible, CVD engineering reference. Former reference product: pyrolytic boron nitride crucible, CVD engineering reference. Activity/product labels and supplier references only; coefficients, formulas, uncertainty, declared output and unit are unchanged. Original engineering assumptions, functional-unit basis and limitations remain below.
 APPROVED PYROLYTIC BORON NITRIDE CRUCIBLE SUPPLY, issue112,2026-10-18. Pallas2020 SI S6 labels pBN crucibles but usesB4C proxy. US4690841A demonstratesCVD BCl3/NH3 ongraphite at&gt;=1900C;EP0851042A2 example usesBCl31L/min,NH34L/min,20h,.8mm deposit. https://patents.google.com/patent/US4690841A/en ; https://data.epo.org/publication-server/rest/v1.2/publication-dates/19980701/patents/EP0851042NWA2/document.pdf . BCl3carbochlorination referencehttps://patents.google.com/patent/US4210631A/en . pBN=BN,notB4C:boronmassfraction=0.4355885078776645 ratherthan0.7826102694973847. ReplaceonlyactivebalancedpolycrystallineGaAsandsinglecrystalgrowthcrucibleinputs atsame.01kg/kg boule withfinishedpBNreference. Oldlegacyunbalancedbouleprovider remainsavailablebutunusedbyactivecrystalgrowth;doNOTdoublecorrectitsunrelatedGaAsfeed. Preserve.01kgcrucibleEOLineachgrowthstage;changingceramicsupplierdoesnotaddanothercrucibleEOL. Existinggenericundergroundhazardoustreatment isfateproxy,notnewrecoverycredit.
@@ -12841,370 +12973,382 @@
         </is>
       </c>
     </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">type</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">processwithreferenceproduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
         <is>
           <t>Exchanges</t>
         </is>
       </c>
     </row>
-    <row r="658">
-      <c r="A658" t="inlineStr">
+    <row r="670">
+      <c r="A670" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B658" t="inlineStr">
+      <c r="B670" t="inlineStr">
         <is>
           <t>amount</t>
         </is>
       </c>
-      <c r="C658" t="inlineStr">
+      <c r="C670" t="inlineStr">
         <is>
           <t>location</t>
         </is>
       </c>
-      <c r="D658" t="inlineStr">
+      <c r="D670" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E658" t="inlineStr">
+      <c r="E670" t="inlineStr">
         <is>
           <t>categories</t>
         </is>
       </c>
-      <c r="F658" t="inlineStr">
+      <c r="F670" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="G658" t="inlineStr">
+      <c r="G670" t="inlineStr">
         <is>
           <t>reference product</t>
         </is>
       </c>
-      <c r="H658" t="inlineStr">
+      <c r="H670" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="I658" t="inlineStr">
+      <c r="I670" t="inlineStr">
         <is>
           <t>product</t>
         </is>
       </c>
     </row>
-    <row r="659">
-      <c r="A659" t="inlineStr">
+    <row r="671">
+      <c r="A671" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible production, chemical vapour deposition</t>
         </is>
       </c>
-      <c r="B659">
-        <v>1</v>
-      </c>
-      <c r="C659" t="inlineStr">
+      <c r="B671">
+        <v>1</v>
+      </c>
+      <c r="C671" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D659" t="inlineStr">
+      <c r="D671" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F659" t="inlineStr">
+      <c r="F671" t="inlineStr">
         <is>
           <t>production</t>
         </is>
       </c>
-      <c r="G659" t="inlineStr">
+      <c r="G671" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
-      <c r="I659" t="inlineStr">
+      <c r="I671" t="inlineStr">
         <is>
           <t xml:space="preserve">pyrolytic boron nitride crucible</t>
         </is>
       </c>
     </row>
-    <row r="660">
-      <c r="A660" t="inlineStr">
+    <row r="672">
+      <c r="A672" t="inlineStr">
         <is>
           <t xml:space="preserve">boron trichloride production, carbochlorination</t>
         </is>
       </c>
-      <c r="B660">
+      <c r="B672">
         <v>9.938857701533118</v>
       </c>
-      <c r="C660" t="inlineStr">
+      <c r="C672" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D660" t="inlineStr">
+      <c r="D672" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F660" t="inlineStr">
+      <c r="F672" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G660" t="inlineStr">
+      <c r="G672" t="inlineStr">
         <is>
           <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
-      <c r="I660" t="inlineStr">
+      <c r="I672" t="inlineStr">
         <is>
           <t xml:space="preserve">boron trichloride</t>
         </is>
       </c>
     </row>
-    <row r="661">
-      <c r="A661" t="inlineStr">
+    <row r="673">
+      <c r="A673" t="inlineStr">
         <is>
           <t>market for ammonia, anhydrous, liquid</t>
         </is>
       </c>
-      <c r="B661">
+      <c r="B673">
         <v>5.7790606184639985</v>
       </c>
-      <c r="C661" t="inlineStr">
+      <c r="C673" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D661" t="inlineStr">
+      <c r="D673" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F661" t="inlineStr">
+      <c r="F673" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G661" t="inlineStr">
+      <c r="G673" t="inlineStr">
         <is>
           <t>ammonia, anhydrous, liquid</t>
         </is>
       </c>
-      <c r="I661" t="inlineStr">
+      <c r="I673" t="inlineStr">
         <is>
           <t>ammonia, anhydrous, liquid</t>
         </is>
       </c>
     </row>
-    <row r="662">
-      <c r="A662" t="inlineStr">
+    <row r="674">
+      <c r="A674" t="inlineStr">
         <is>
           <t>market for sulfuric acid</t>
         </is>
       </c>
-      <c r="B662">
+      <c r="B674">
         <v>2.0798985415345594</v>
       </c>
-      <c r="C662" t="inlineStr">
+      <c r="C674" t="inlineStr">
         <is>
           <t>RER</t>
         </is>
       </c>
-      <c r="D662" t="inlineStr">
+      <c r="D674" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F662" t="inlineStr">
+      <c r="F674" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G662" t="inlineStr">
+      <c r="G674" t="inlineStr">
         <is>
           <t>sulfuric acid</t>
         </is>
       </c>
-      <c r="I662" t="inlineStr">
+      <c r="I674" t="inlineStr">
         <is>
           <t>sulfuric acid</t>
         </is>
       </c>
     </row>
-    <row r="663">
-      <c r="A663" t="inlineStr">
+    <row r="675">
+      <c r="A675" t="inlineStr">
         <is>
           <t>market for tap water</t>
         </is>
       </c>
-      <c r="B663">
+      <c r="B675">
         <v>102.29235901536086</v>
       </c>
-      <c r="C663" t="inlineStr">
+      <c r="C675" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D663" t="inlineStr">
+      <c r="D675" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F663" t="inlineStr">
+      <c r="F675" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G663" t="inlineStr">
+      <c r="G675" t="inlineStr">
         <is>
           <t>tap water</t>
         </is>
       </c>
-      <c r="I663" t="inlineStr">
+      <c r="I675" t="inlineStr">
         <is>
           <t>tap water</t>
         </is>
       </c>
     </row>
-    <row r="664">
-      <c r="A664" t="inlineStr">
+    <row r="676">
+      <c r="A676" t="inlineStr">
         <is>
           <t>market for graphite</t>
         </is>
       </c>
-      <c r="B664">
+      <c r="B676">
         <v>0.02</v>
       </c>
-      <c r="C664" t="inlineStr">
+      <c r="C676" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D664" t="inlineStr">
+      <c r="D676" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F664" t="inlineStr">
+      <c r="F676" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G664" t="inlineStr">
+      <c r="G676" t="inlineStr">
         <is>
           <t>graphite</t>
         </is>
       </c>
-      <c r="I664" t="inlineStr">
+      <c r="I676" t="inlineStr">
         <is>
           <t>graphite</t>
         </is>
       </c>
     </row>
-    <row r="665">
-      <c r="A665" t="inlineStr">
+    <row r="677">
+      <c r="A677" t="inlineStr">
         <is>
           <t>market group for electricity, medium voltage</t>
         </is>
       </c>
-      <c r="B665">
+      <c r="B677">
         <v>250</v>
       </c>
-      <c r="C665" t="inlineStr">
+      <c r="C677" t="inlineStr">
         <is>
           <t>GLO</t>
         </is>
       </c>
-      <c r="D665" t="inlineStr">
+      <c r="D677" t="inlineStr">
         <is>
           <t>kilowatt hour</t>
         </is>
       </c>
-      <c r="F665" t="inlineStr">
+      <c r="F677" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G665" t="inlineStr">
+      <c r="G677" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>
       </c>
-      <c r="I665" t="inlineStr">
+      <c r="I677" t="inlineStr">
         <is>
           <t>electricity, medium voltage</t>
         </is>
       </c>
     </row>
-    <row r="666">
-      <c r="A666" t="inlineStr">
+    <row r="678">
+      <c r="A678" t="inlineStr">
         <is>
           <t>market for wastewater, average</t>
         </is>
       </c>
-      <c r="B666">
+      <c r="B678">
         <v>-0.10821594936176834</v>
       </c>
-      <c r="C666" t="inlineStr">
+      <c r="C678" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D666" t="inlineStr">
+      <c r="D678" t="inlineStr">
         <is>
           <t>cubic meter</t>
         </is>
       </c>
-      <c r="F666" t="inlineStr">
+      <c r="F678" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G666" t="inlineStr">
+      <c r="G678" t="inlineStr">
         <is>
           <t>wastewater, average</t>
         </is>
       </c>
-      <c r="I666" t="inlineStr">
+      <c r="I678" t="inlineStr">
         <is>
           <t>wastewater, average</t>
         </is>
       </c>
     </row>
-    <row r="667">
-      <c r="A667" t="inlineStr">
+    <row r="679">
+      <c r="A679" t="inlineStr">
         <is>
           <t>market for inert waste, for final disposal</t>
         </is>
       </c>
-      <c r="B667">
+      <c r="B679">
         <v>-0.07263157894736837</v>
       </c>
-      <c r="C667" t="inlineStr">
+      <c r="C679" t="inlineStr">
         <is>
           <t>RoW</t>
         </is>
       </c>
-      <c r="D667" t="inlineStr">
+      <c r="D679" t="inlineStr">
         <is>
           <t>kilogram</t>
         </is>
       </c>
-      <c r="F667" t="inlineStr">
+      <c r="F679" t="inlineStr">
         <is>
           <t>technosphere</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
+      <c r="G679" t="inlineStr">
         <is>
           <t>inert waste, for final disposal</t>
         </is>
       </c>
-      <c r="I667" t="inlineStr">
+      <c r="I679" t="inlineStr">
         <is>
           <t>inert waste, for final disposal</t>
         </is>
